--- a/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,68 +429,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>country</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>competition</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>capacity</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>id_team_home</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>id_team_away</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>id_country</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>id_competition</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>is_cup</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>season</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -507,1748 +507,2376 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
+          <t>zuzbQnCF</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>45527.64583333334</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>54042</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>59</v>
+      </c>
+      <c r="I2" t="n">
+        <v>591</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>YZZcMwBs</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45528.4375</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>30660</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>59</v>
+      </c>
+      <c r="I3" t="n">
+        <v>591</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>GbeXvnR8</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45528.4375</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>34700</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>59</v>
+      </c>
+      <c r="I4" t="n">
+        <v>591</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>O48oHrZ1</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45528.4375</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>30150</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>59</v>
+      </c>
+      <c r="I5" t="n">
+        <v>591</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2FREIeA6</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45528.4375</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>59</v>
+      </c>
+      <c r="I6" t="n">
+        <v>591</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>dfO6OQtS</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45528.4375</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>47069</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>59</v>
+      </c>
+      <c r="I7" t="n">
+        <v>591</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>SxFxJ44k</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45528.5625</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>81365</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>59</v>
+      </c>
+      <c r="I8" t="n">
+        <v>591</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>t0w6KHuf</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45529.4375</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>28917</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>59</v>
+      </c>
+      <c r="I9" t="n">
+        <v>591</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AuVMGZvJ</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45529.52083333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>29546</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I10" t="n">
+        <v>591</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>pWQQJq6l</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
+      <c r="B11" s="2" t="n">
         <v>45520.54166666666</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">leuna chemie stadion
   halle </t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="E11" t="n">
         <v>15057</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>boX3cIQa</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>ILyJuN3g</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>59</v>
-      </c>
-      <c r="K2" t="n">
-        <v>593</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="H11" t="n">
+        <v>59</v>
+      </c>
+      <c r="I11" t="n">
+        <v>593</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
         <is>
           <t>v9k3aY5F</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>hIsO3XFj</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
+      <c r="B12" s="2" t="n">
         <v>45520.54166666666</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
         <is>
           <t xml:space="preserve">brita arena
   wiesbaden </t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="E12" t="n">
         <v>12566</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>ObxFt3lm</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>EuakNmc1</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>59</v>
-      </c>
-      <c r="K3" t="n">
-        <v>593</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="H12" t="n">
+        <v>59</v>
+      </c>
+      <c r="I12" t="n">
+        <v>593</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>EuakNmc1</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>8vndvXTk</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>EF8gXauC</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
+      <c r="B13" s="2" t="n">
         <v>45520.54166666666</v>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
         <is>
           <t xml:space="preserve">flyeralarm arena
   wurzburger </t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="E13" t="n">
         <v>13090</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>nVM1YUFj</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>hQAtP9Sl</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>59</v>
-      </c>
-      <c r="K4" t="n">
-        <v>593</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="H13" t="n">
+        <v>59</v>
+      </c>
+      <c r="I13" t="n">
+        <v>593</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
         <is>
           <t>nJQmYp1B</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>lONsG15D</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
+      <c r="B14" s="2" t="n">
         <v>45520.65625</v>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t xml:space="preserve">donaustadion
   ulm </t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="E14" t="n">
         <v>19500</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>tbC3EcQn</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>nVp0wiqd</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>59</v>
-      </c>
-      <c r="K5" t="n">
-        <v>593</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="H14" t="n">
+        <v>59</v>
+      </c>
+      <c r="I14" t="n">
+        <v>593</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>0K2qBFNG</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
+      <c r="B15" s="2" t="n">
         <v>45521.33333333334</v>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
         <is>
           <t xml:space="preserve">erzgebirgsstadion
   aue </t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="E15" t="n">
         <v>16485</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>vsXIDreP</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>88HSzjDr</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>59</v>
-      </c>
-      <c r="K6" t="n">
-        <v>593</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="H15" t="n">
+        <v>59</v>
+      </c>
+      <c r="I15" t="n">
+        <v>593</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
         <is>
           <t>WG9pOTse</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Kj4sifWp</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
+      <c r="B16" s="2" t="n">
         <v>45521.33333333334</v>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bruchwegstadion
+  mainz </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>7134</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>WzEYqEyg</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>CCQGbik8</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>59</v>
-      </c>
-      <c r="K7" t="n">
-        <v>593</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="H16" t="n">
+        <v>59</v>
+      </c>
+      <c r="I16" t="n">
+        <v>593</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
         <is>
           <t>6FDqshzF</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>bF2q76Mr</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
+      <c r="B17" s="2" t="n">
         <v>45521.4375</v>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
         <is>
           <t xml:space="preserve">ostalb arena
   aalen </t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="E17" t="n">
         <v>14500</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Oh2C15j0</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>0Ija0Ej9</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>59</v>
-      </c>
-      <c r="K8" t="n">
-        <v>593</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="H17" t="n">
+        <v>59</v>
+      </c>
+      <c r="I17" t="n">
+        <v>593</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
         <is>
           <t>nP1i5US1</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>vyk5gjdE</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
+      <c r="B18" s="2" t="n">
         <v>45521.4375</v>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t xml:space="preserve">volksstadion greifswald
   greifswald </t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="E18" t="n">
         <v>4990</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Q1yNyI5t</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>pzHW4oaE</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>59</v>
-      </c>
-      <c r="K9" t="n">
-        <v>593</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="H18" t="n">
+        <v>59</v>
+      </c>
+      <c r="I18" t="n">
+        <v>593</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>tbKZHNz1</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
+      <c r="B19" s="2" t="n">
         <v>45521.4375</v>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
         <is>
           <t xml:space="preserve">audi sportpark
   ingolstadt </t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="E19" t="n">
         <v>15800</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>ne5QkLtB</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>naWckLmC</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>59</v>
-      </c>
-      <c r="K10" t="n">
-        <v>593</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="H19" t="n">
+        <v>59</v>
+      </c>
+      <c r="I19" t="n">
+        <v>593</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>MZjh9ghT</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
+      <c r="B20" s="2" t="n">
         <v>45521.4375</v>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
         <is>
           <t xml:space="preserve">stadion an der hafenstrasse
   essen </t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="E20" t="n">
         <v>20352</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>EB0xsr77</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>KbS1suSm</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>59</v>
-      </c>
-      <c r="K11" t="n">
-        <v>593</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
+      <c r="H20" t="n">
+        <v>59</v>
+      </c>
+      <c r="I20" t="n">
+        <v>593</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
         <is>
           <t>nP1i5US1</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>f1nnRRDE</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
+      <c r="B21" s="2" t="n">
         <v>45521.4375</v>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
         <is>
           <t xml:space="preserve">stadion an der bremer bruck
   osnabruck </t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="E21" t="n">
         <v>16667</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>88Xgj1Y5</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>fiEQZ7C7</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>59</v>
-      </c>
-      <c r="K12" t="n">
-        <v>593</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
+      <c r="H21" t="n">
+        <v>59</v>
+      </c>
+      <c r="I21" t="n">
+        <v>593</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
         <is>
           <t>nJQmYp1B</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>8QPARz8c</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
+      <c r="B22" s="2" t="n">
         <v>45521.4375</v>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
         <is>
           <t xml:space="preserve">ms technologie arena
   villingen schwenningen </t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="E22" t="n">
         <v>8000</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>lKLJUxeT</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>KWixEVWi</t>
         </is>
       </c>
-      <c r="J13" t="n">
-        <v>59</v>
-      </c>
-      <c r="K13" t="n">
-        <v>593</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="H22" t="n">
+        <v>59</v>
+      </c>
+      <c r="I22" t="n">
+        <v>593</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>hzyf0b9b</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
+      <c r="B23" s="2" t="n">
         <v>45521.54166666666</v>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
         <is>
           <t xml:space="preserve">new tivoli
   aachen </t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="E23" t="n">
         <v>31026</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>j3PKcB4E</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>63WsD2ei</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v>59</v>
-      </c>
-      <c r="K14" t="n">
-        <v>593</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
+      <c r="H23" t="n">
+        <v>59</v>
+      </c>
+      <c r="I23" t="n">
+        <v>593</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
         <is>
           <t>ILyJuN3g</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>CpiTEcOi</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
+      <c r="B24" s="2" t="n">
         <v>45521.54166666666</v>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
         <is>
           <t xml:space="preserve">schuco arena
   bielefeld </t>
         </is>
       </c>
-      <c r="G15" t="n">
+      <c r="E24" t="n">
         <v>27332</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>pp38UXK8</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>dfNCCCzS</t>
         </is>
       </c>
-      <c r="J15" t="n">
-        <v>59</v>
-      </c>
-      <c r="K15" t="n">
-        <v>593</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
+      <c r="H24" t="n">
+        <v>59</v>
+      </c>
+      <c r="I24" t="n">
+        <v>593</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
         <is>
           <t>QqLCC3il</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>8CpxDyg4</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
+      <c r="B25" s="2" t="n">
         <v>45521.54166666666</v>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
         <is>
           <t xml:space="preserve">stadion lohmuhle
   lubeck </t>
         </is>
       </c>
-      <c r="G16" t="n">
+      <c r="E25" t="n">
         <v>17849</v>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>I1Vk6k3R</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>nP1i5US1</t>
         </is>
       </c>
-      <c r="J16" t="n">
-        <v>59</v>
-      </c>
-      <c r="K16" t="n">
-        <v>593</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
+      <c r="H25" t="n">
+        <v>59</v>
+      </c>
+      <c r="I25" t="n">
+        <v>593</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
         <is>
           <t>0Ija0Ej9</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>6q2yrHgU</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
+      <c r="B26" s="2" t="n">
         <v>45522.33333333334</v>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
         <is>
           <t xml:space="preserve">ludwigspark stadion
   saarbrucken </t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="E26" t="n">
         <v>16003</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>fLbhmJ5l</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>6FDqshzF</t>
         </is>
       </c>
-      <c r="J17" t="n">
-        <v>59</v>
-      </c>
-      <c r="K17" t="n">
-        <v>593</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
+      <c r="H26" t="n">
+        <v>59</v>
+      </c>
+      <c r="I26" t="n">
+        <v>593</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
         <is>
           <t>CCQGbik8</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>AiJ3kset</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
+      <c r="B27" s="2" t="n">
         <v>45522.33333333334</v>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">friedrich ludwig jahn sportpark
+  berlin </t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>19708</v>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>UNr2EUfd</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>fTVNku3I</t>
         </is>
       </c>
-      <c r="J18" t="n">
-        <v>59</v>
-      </c>
-      <c r="K18" t="n">
-        <v>593</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="H27" t="n">
+        <v>59</v>
+      </c>
+      <c r="I27" t="n">
+        <v>593</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>YV3TqwPH</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
+      <c r="B28" s="2" t="n">
         <v>45522.4375</v>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion am panzenberg
+  bremen </t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>tW75B1ei</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>G2Op923t</t>
         </is>
       </c>
-      <c r="J19" t="n">
-        <v>59</v>
-      </c>
-      <c r="K19" t="n">
-        <v>593</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="H28" t="n">
+        <v>59</v>
+      </c>
+      <c r="I28" t="n">
+        <v>593</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>l0ueP5rR</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
+      <c r="B29" s="2" t="n">
         <v>45522.4375</v>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
         <is>
           <t xml:space="preserve">ostseestadion
   rostock </t>
         </is>
       </c>
-      <c r="G20" t="n">
+      <c r="E29" t="n">
         <v>29000</v>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>KIHmtCkL</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>2y0u8Wrq</t>
         </is>
       </c>
-      <c r="J20" t="n">
-        <v>59</v>
-      </c>
-      <c r="K20" t="n">
-        <v>593</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N20" t="inlineStr">
+      <c r="H29" t="n">
+        <v>59</v>
+      </c>
+      <c r="I29" t="n">
+        <v>593</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>ILyJuN3g</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="O29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>t2AoZLAa</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
+      <c r="B30" s="2" t="n">
         <v>45522.4375</v>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
         <is>
           <t xml:space="preserve">friedrich ebert stadium
   hildesheim </t>
         </is>
       </c>
-      <c r="G21" t="n">
+      <c r="E30" t="n">
         <v>10000</v>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>E3xs5mIe</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>6in2Eknb</t>
         </is>
       </c>
-      <c r="J21" t="n">
-        <v>59</v>
-      </c>
-      <c r="K21" t="n">
-        <v>593</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="H30" t="n">
+        <v>59</v>
+      </c>
+      <c r="I30" t="n">
+        <v>593</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>jFMCm08e</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
+      <c r="B31" s="2" t="n">
         <v>45522.4375</v>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
         <is>
           <t xml:space="preserve">jahnstadion regensburg
   regensburg </t>
         </is>
       </c>
-      <c r="G22" t="n">
+      <c r="E31" t="n">
         <v>15210</v>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>UiCmEP56</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>8Y2m6ADe</t>
         </is>
       </c>
-      <c r="J22" t="n">
-        <v>59</v>
-      </c>
-      <c r="K22" t="n">
-        <v>593</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr">
+      <c r="H31" t="n">
+        <v>59</v>
+      </c>
+      <c r="I31" t="n">
+        <v>593</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
         <is>
           <t>0Ija0Ej9</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>tvOIPExA</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
+      <c r="B32" s="2" t="n">
         <v>45522.4375</v>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
         <is>
           <t xml:space="preserve">hardtwaldstadion
   sandhausen </t>
         </is>
       </c>
-      <c r="G23" t="n">
+      <c r="E32" t="n">
         <v>15414</v>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>UZxEj1R4</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>WG9pOTse</t>
         </is>
       </c>
-      <c r="J23" t="n">
-        <v>59</v>
-      </c>
-      <c r="K23" t="n">
-        <v>593</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr">
+      <c r="H32" t="n">
+        <v>59</v>
+      </c>
+      <c r="I32" t="n">
+        <v>593</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
         <is>
           <t>88HSzjDr</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>KSwfVwAO</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
+      <c r="B33" s="2" t="n">
         <v>45522.4375</v>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>29546</v>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>WrbkcjCd</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>S0hPB9rA</t>
         </is>
       </c>
-      <c r="J24" t="n">
-        <v>59</v>
-      </c>
-      <c r="K24" t="n">
-        <v>593</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr">
+      <c r="H33" t="n">
+        <v>59</v>
+      </c>
+      <c r="I33" t="n">
+        <v>593</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
         <is>
           <t>8vndvXTk</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t>pzHxyrtm</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
+      <c r="B34" s="2" t="n">
         <v>45522.54166666666</v>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
         <is>
           <t xml:space="preserve">stadion am lotter kreuz
   lotte </t>
         </is>
       </c>
-      <c r="G25" t="n">
+      <c r="E34" t="n">
         <v>10059</v>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>hjNlCFPB</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>EB3q7jbk</t>
         </is>
       </c>
-      <c r="J25" t="n">
-        <v>59</v>
-      </c>
-      <c r="K25" t="n">
-        <v>593</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr">
+      <c r="H34" t="n">
+        <v>59</v>
+      </c>
+      <c r="I34" t="n">
+        <v>593</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
         <is>
           <t>naWckLmC</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
         <is>
           <t>dCPKovw8</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
+      <c r="B35" s="2" t="n">
         <v>45522.54166666666</v>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
         <is>
           <t xml:space="preserve">hansch arena
   meppen </t>
         </is>
       </c>
-      <c r="G26" t="n">
+      <c r="E35" t="n">
         <v>13696</v>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>rXqBh2xP</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>v9k3aY5F</t>
         </is>
       </c>
-      <c r="J26" t="n">
-        <v>59</v>
-      </c>
-      <c r="K26" t="n">
-        <v>593</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
+      <c r="H35" t="n">
+        <v>59</v>
+      </c>
+      <c r="I35" t="n">
+        <v>593</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
         <is>
           <t>ILyJuN3g</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t>vXAKoaf5</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
+      <c r="B36" s="2" t="n">
         <v>45522.54166666666</v>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
         <is>
           <t xml:space="preserve">rudolf harbig stadion
   dresden </t>
         </is>
       </c>
-      <c r="G27" t="n">
+      <c r="E36" t="n">
         <v>32249</v>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>zL1YsOi1</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>ne1oL3y7</t>
         </is>
       </c>
-      <c r="J27" t="n">
-        <v>59</v>
-      </c>
-      <c r="K27" t="n">
-        <v>593</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr">
+      <c r="H36" t="n">
+        <v>59</v>
+      </c>
+      <c r="I36" t="n">
+        <v>593</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
         <is>
           <t>WG9pOTse</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
         <is>
           <t>06NAdG8N</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
+      <c r="B37" s="2" t="n">
         <v>45523.54166666666</v>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
         <is>
           <t xml:space="preserve">stadion der freundschaft
   cottbus </t>
         </is>
       </c>
-      <c r="G28" t="n">
+      <c r="E37" t="n">
         <v>22450</v>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>6g44VD52</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Ig1f1fy3</t>
         </is>
       </c>
-      <c r="J28" t="n">
-        <v>59</v>
-      </c>
-      <c r="K28" t="n">
-        <v>593</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
+      <c r="H37" t="n">
+        <v>59</v>
+      </c>
+      <c r="I37" t="n">
+        <v>593</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
         <is>
           <t>v9k3aY5F</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
         <is>
           <t>Sff03OL7</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
+      <c r="B38" s="2" t="n">
         <v>45523.54166666666</v>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
         <is>
           <t xml:space="preserve">bieberer berg stadion
   offenbach am main </t>
         </is>
       </c>
-      <c r="G29" t="n">
+      <c r="E38" t="n">
         <v>20500</v>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>YJURlaIO</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>YFuz2RLm</t>
         </is>
       </c>
-      <c r="J29" t="n">
-        <v>59</v>
-      </c>
-      <c r="K29" t="n">
-        <v>593</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="H38" t="n">
+        <v>59</v>
+      </c>
+      <c r="I38" t="n">
+        <v>593</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
         <is>
           <t>EkP2bxvB</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n">
+      <c r="B39" s="2" t="n">
         <v>45523.54166666666</v>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
         <is>
           <t xml:space="preserve">stadion oberwerth
   koblenz </t>
         </is>
       </c>
-      <c r="G30" t="n">
+      <c r="E39" t="n">
         <v>9500</v>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>p8wBsqZt</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>nwkTahLL</t>
         </is>
       </c>
-      <c r="J30" t="n">
-        <v>59</v>
-      </c>
-      <c r="K30" t="n">
-        <v>593</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr">
+      <c r="H39" t="n">
+        <v>59</v>
+      </c>
+      <c r="I39" t="n">
+        <v>593</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
         <is>
           <t>dfNCCCzS</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
         <is>
           <t>pAXo2Kvn</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n">
+      <c r="B40" s="2" t="n">
         <v>45523.65625</v>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
         <is>
           <t xml:space="preserve">eintracht stadion
   braunschweig </t>
         </is>
       </c>
-      <c r="G31" t="n">
+      <c r="E40" t="n">
         <v>23325</v>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>QqLCC3il</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>8vndvXTk</t>
         </is>
       </c>
-      <c r="J31" t="n">
-        <v>59</v>
-      </c>
-      <c r="K31" t="n">
-        <v>593</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N31" t="inlineStr">
+      <c r="H40" t="n">
+        <v>59</v>
+      </c>
+      <c r="I40" t="n">
+        <v>593</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>dfNCCCzS</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>EuakNmc1</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>W67CmLPh</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45531.65625</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">preussenstadion
+  munster </t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>12794</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>zedZaSL7</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>59</v>
+      </c>
+      <c r="I41" t="n">
+        <v>593</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
         <is>
           <t>fcxqFy2l</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>super cup</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n">
+      <c r="B42" s="2" t="n">
         <v>45521.64583333334</v>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
         <is>
           <t xml:space="preserve">bayarena
   leverkusen </t>
         </is>
       </c>
-      <c r="G32" t="n">
+      <c r="E42" t="n">
         <v>30210</v>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>4jcj2zMd</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>nJQmYp1B</t>
         </is>
       </c>
-      <c r="J32" t="n">
-        <v>59</v>
-      </c>
-      <c r="K32" t="n">
+      <c r="H42" t="n">
+        <v>59</v>
+      </c>
+      <c r="I42" t="n">
         <v>594</v>
       </c>
-      <c r="L32" t="n">
-        <v>1</v>
-      </c>
-      <c r="M32" t="n">
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
         <v>2024</v>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>super cup</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>WG9pOTse</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>fiEQZ7C7</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,1776 +569,2256 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>YZZcMwBs</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45528.4375</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>30660</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>59</v>
+      </c>
+      <c r="I3" t="n">
+        <v>591</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>GbeXvnR8</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45528.4375</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>34700</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>59</v>
+      </c>
+      <c r="I4" t="n">
+        <v>591</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>O48oHrZ1</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45528.4375</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>30150</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>59</v>
+      </c>
+      <c r="I5" t="n">
+        <v>591</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2FREIeA6</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45528.4375</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>59</v>
+      </c>
+      <c r="I6" t="n">
+        <v>591</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>dfO6OQtS</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45528.4375</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>47069</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>59</v>
+      </c>
+      <c r="I7" t="n">
+        <v>591</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>SxFxJ44k</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45528.5625</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>81365</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>59</v>
+      </c>
+      <c r="I8" t="n">
+        <v>591</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>t0w6KHuf</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45529.4375</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>28917</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>59</v>
+      </c>
+      <c r="I9" t="n">
+        <v>591</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AuVMGZvJ</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45529.52083333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>29546</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I10" t="n">
+        <v>591</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>pWQQJq6l</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45520.54166666666</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
           <t xml:space="preserve">leuna chemie stadion
   halle </t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E11" t="n">
         <v>15057</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>boX3cIQa</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>ILyJuN3g</t>
         </is>
       </c>
-      <c r="H3" t="n">
-        <v>59</v>
-      </c>
-      <c r="I3" t="n">
-        <v>593</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="H11" t="n">
+        <v>59</v>
+      </c>
+      <c r="I11" t="n">
+        <v>593</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
         <is>
           <t>v9k3aY5F</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>hIsO3XFj</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B12" s="2" t="n">
         <v>45520.54166666666</v>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
         <is>
           <t xml:space="preserve">brita arena
   wiesbaden </t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E12" t="n">
         <v>12566</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>ObxFt3lm</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>EuakNmc1</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>59</v>
-      </c>
-      <c r="I4" t="n">
-        <v>593</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="H12" t="n">
+        <v>59</v>
+      </c>
+      <c r="I12" t="n">
+        <v>593</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>EuakNmc1</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>8vndvXTk</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>EF8gXauC</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B13" s="2" t="n">
         <v>45520.54166666666</v>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
         <is>
           <t xml:space="preserve">flyeralarm arena
   wurzburger </t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E13" t="n">
         <v>13090</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>nVM1YUFj</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>hQAtP9Sl</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>59</v>
-      </c>
-      <c r="I5" t="n">
-        <v>593</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="H13" t="n">
+        <v>59</v>
+      </c>
+      <c r="I13" t="n">
+        <v>593</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
         <is>
           <t>nJQmYp1B</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>lONsG15D</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B14" s="2" t="n">
         <v>45520.65625</v>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t xml:space="preserve">donaustadion
   ulm </t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E14" t="n">
         <v>19500</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>tbC3EcQn</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>nVp0wiqd</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>59</v>
-      </c>
-      <c r="I6" t="n">
-        <v>593</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="H14" t="n">
+        <v>59</v>
+      </c>
+      <c r="I14" t="n">
+        <v>593</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>0K2qBFNG</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B15" s="2" t="n">
         <v>45521.33333333334</v>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
         <is>
           <t xml:space="preserve">erzgebirgsstadion
   aue </t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E15" t="n">
         <v>16485</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>vsXIDreP</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>88HSzjDr</t>
         </is>
       </c>
-      <c r="H7" t="n">
-        <v>59</v>
-      </c>
-      <c r="I7" t="n">
-        <v>593</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="H15" t="n">
+        <v>59</v>
+      </c>
+      <c r="I15" t="n">
+        <v>593</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
         <is>
           <t>WG9pOTse</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Kj4sifWp</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B16" s="2" t="n">
         <v>45521.33333333334</v>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t xml:space="preserve">bruchwegstadion
   mainz </t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E16" t="n">
         <v>7134</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>WzEYqEyg</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>CCQGbik8</t>
         </is>
       </c>
-      <c r="H8" t="n">
-        <v>59</v>
-      </c>
-      <c r="I8" t="n">
-        <v>593</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="H16" t="n">
+        <v>59</v>
+      </c>
+      <c r="I16" t="n">
+        <v>593</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
         <is>
           <t>6FDqshzF</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>bF2q76Mr</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B17" s="2" t="n">
         <v>45521.4375</v>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
         <is>
           <t xml:space="preserve">ostalb arena
   aalen </t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E17" t="n">
         <v>14500</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Oh2C15j0</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>0Ija0Ej9</t>
         </is>
       </c>
-      <c r="H9" t="n">
-        <v>59</v>
-      </c>
-      <c r="I9" t="n">
-        <v>593</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+      <c r="H17" t="n">
+        <v>59</v>
+      </c>
+      <c r="I17" t="n">
+        <v>593</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
         <is>
           <t>nP1i5US1</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>vyk5gjdE</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B18" s="2" t="n">
         <v>45521.4375</v>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t xml:space="preserve">volksstadion greifswald
   greifswald </t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E18" t="n">
         <v>4990</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Q1yNyI5t</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>pzHW4oaE</t>
         </is>
       </c>
-      <c r="H10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I10" t="n">
-        <v>593</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="H18" t="n">
+        <v>59</v>
+      </c>
+      <c r="I18" t="n">
+        <v>593</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>tbKZHNz1</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B19" s="2" t="n">
         <v>45521.4375</v>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
         <is>
           <t xml:space="preserve">audi sportpark
   ingolstadt </t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E19" t="n">
         <v>15800</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>ne5QkLtB</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>naWckLmC</t>
         </is>
       </c>
-      <c r="H11" t="n">
-        <v>59</v>
-      </c>
-      <c r="I11" t="n">
-        <v>593</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="H19" t="n">
+        <v>59</v>
+      </c>
+      <c r="I19" t="n">
+        <v>593</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>MZjh9ghT</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B20" s="2" t="n">
         <v>45521.4375</v>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
         <is>
           <t xml:space="preserve">stadion an der hafenstrasse
   essen </t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E20" t="n">
         <v>20352</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>EB0xsr77</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>KbS1suSm</t>
         </is>
       </c>
-      <c r="H12" t="n">
-        <v>59</v>
-      </c>
-      <c r="I12" t="n">
-        <v>593</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
+      <c r="H20" t="n">
+        <v>59</v>
+      </c>
+      <c r="I20" t="n">
+        <v>593</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
         <is>
           <t>nP1i5US1</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>f1nnRRDE</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B21" s="2" t="n">
         <v>45521.4375</v>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
         <is>
           <t xml:space="preserve">stadion an der bremer bruck
   osnabruck </t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E21" t="n">
         <v>16667</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>88Xgj1Y5</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>fiEQZ7C7</t>
         </is>
       </c>
-      <c r="H13" t="n">
-        <v>59</v>
-      </c>
-      <c r="I13" t="n">
-        <v>593</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
+      <c r="H21" t="n">
+        <v>59</v>
+      </c>
+      <c r="I21" t="n">
+        <v>593</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
         <is>
           <t>nJQmYp1B</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>8QPARz8c</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B22" s="2" t="n">
         <v>45521.4375</v>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
         <is>
           <t xml:space="preserve">ms technologie arena
   villingen schwenningen </t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E22" t="n">
         <v>8000</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>lKLJUxeT</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>KWixEVWi</t>
         </is>
       </c>
-      <c r="H14" t="n">
-        <v>59</v>
-      </c>
-      <c r="I14" t="n">
-        <v>593</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="H22" t="n">
+        <v>59</v>
+      </c>
+      <c r="I22" t="n">
+        <v>593</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>hzyf0b9b</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B23" s="2" t="n">
         <v>45521.54166666666</v>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
         <is>
           <t xml:space="preserve">new tivoli
   aachen </t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E23" t="n">
         <v>31026</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>j3PKcB4E</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>63WsD2ei</t>
         </is>
       </c>
-      <c r="H15" t="n">
-        <v>59</v>
-      </c>
-      <c r="I15" t="n">
-        <v>593</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
+      <c r="H23" t="n">
+        <v>59</v>
+      </c>
+      <c r="I23" t="n">
+        <v>593</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
         <is>
           <t>ILyJuN3g</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>CpiTEcOi</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B24" s="2" t="n">
         <v>45521.54166666666</v>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
         <is>
           <t xml:space="preserve">schuco arena
   bielefeld </t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E24" t="n">
         <v>27332</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>pp38UXK8</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>dfNCCCzS</t>
         </is>
       </c>
-      <c r="H16" t="n">
-        <v>59</v>
-      </c>
-      <c r="I16" t="n">
-        <v>593</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
+      <c r="H24" t="n">
+        <v>59</v>
+      </c>
+      <c r="I24" t="n">
+        <v>593</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
         <is>
           <t>QqLCC3il</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>8CpxDyg4</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B25" s="2" t="n">
         <v>45521.54166666666</v>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
         <is>
           <t xml:space="preserve">stadion lohmuhle
   lubeck </t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E25" t="n">
         <v>17849</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>I1Vk6k3R</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>nP1i5US1</t>
         </is>
       </c>
-      <c r="H17" t="n">
-        <v>59</v>
-      </c>
-      <c r="I17" t="n">
-        <v>593</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
+      <c r="H25" t="n">
+        <v>59</v>
+      </c>
+      <c r="I25" t="n">
+        <v>593</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
         <is>
           <t>0Ija0Ej9</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>6q2yrHgU</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B26" s="2" t="n">
         <v>45522.33333333334</v>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
         <is>
           <t xml:space="preserve">ludwigspark stadion
   saarbrucken </t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E26" t="n">
         <v>16003</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>fLbhmJ5l</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>6FDqshzF</t>
         </is>
       </c>
-      <c r="H18" t="n">
-        <v>59</v>
-      </c>
-      <c r="I18" t="n">
-        <v>593</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
+      <c r="H26" t="n">
+        <v>59</v>
+      </c>
+      <c r="I26" t="n">
+        <v>593</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
         <is>
           <t>CCQGbik8</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>AiJ3kset</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B27" s="2" t="n">
         <v>45522.33333333334</v>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
         <is>
           <t xml:space="preserve">friedrich ludwig jahn sportpark
   berlin </t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E27" t="n">
         <v>19708</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>UNr2EUfd</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>fTVNku3I</t>
         </is>
       </c>
-      <c r="H19" t="n">
-        <v>59</v>
-      </c>
-      <c r="I19" t="n">
-        <v>593</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="H27" t="n">
+        <v>59</v>
+      </c>
+      <c r="I27" t="n">
+        <v>593</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>YV3TqwPH</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B28" s="2" t="n">
         <v>45522.4375</v>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
         <is>
           <t xml:space="preserve">stadion am panzenberg
   bremen </t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="E28" t="n">
         <v>5000</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>tW75B1ei</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>G2Op923t</t>
         </is>
       </c>
-      <c r="H20" t="n">
-        <v>59</v>
-      </c>
-      <c r="I20" t="n">
-        <v>593</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="H28" t="n">
+        <v>59</v>
+      </c>
+      <c r="I28" t="n">
+        <v>593</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>l0ueP5rR</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B29" s="2" t="n">
         <v>45522.4375</v>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
         <is>
           <t xml:space="preserve">ostseestadion
   rostock </t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="E29" t="n">
         <v>29000</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>KIHmtCkL</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>2y0u8Wrq</t>
         </is>
       </c>
-      <c r="H21" t="n">
-        <v>59</v>
-      </c>
-      <c r="I21" t="n">
-        <v>593</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
+      <c r="H29" t="n">
+        <v>59</v>
+      </c>
+      <c r="I29" t="n">
+        <v>593</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>ILyJuN3g</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="O29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>t2AoZLAa</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B30" s="2" t="n">
         <v>45522.4375</v>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
         <is>
           <t xml:space="preserve">friedrich ebert stadium
   hildesheim </t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="E30" t="n">
         <v>10000</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>E3xs5mIe</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>6in2Eknb</t>
         </is>
       </c>
-      <c r="H22" t="n">
-        <v>59</v>
-      </c>
-      <c r="I22" t="n">
-        <v>593</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="H30" t="n">
+        <v>59</v>
+      </c>
+      <c r="I30" t="n">
+        <v>593</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>jFMCm08e</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="B31" s="2" t="n">
         <v>45522.4375</v>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
         <is>
           <t xml:space="preserve">jahnstadion regensburg
   regensburg </t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="E31" t="n">
         <v>15210</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>UiCmEP56</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>8Y2m6ADe</t>
         </is>
       </c>
-      <c r="H23" t="n">
-        <v>59</v>
-      </c>
-      <c r="I23" t="n">
-        <v>593</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr">
+      <c r="H31" t="n">
+        <v>59</v>
+      </c>
+      <c r="I31" t="n">
+        <v>593</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
         <is>
           <t>0Ija0Ej9</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>tvOIPExA</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B32" s="2" t="n">
         <v>45522.4375</v>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
         <is>
           <t xml:space="preserve">hardtwaldstadion
   sandhausen </t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="E32" t="n">
         <v>15414</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>UZxEj1R4</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>WG9pOTse</t>
         </is>
       </c>
-      <c r="H24" t="n">
-        <v>59</v>
-      </c>
-      <c r="I24" t="n">
-        <v>593</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr">
+      <c r="H32" t="n">
+        <v>59</v>
+      </c>
+      <c r="I32" t="n">
+        <v>593</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
         <is>
           <t>88HSzjDr</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>KSwfVwAO</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n">
+      <c r="B33" s="2" t="n">
         <v>45522.4375</v>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
         <is>
           <t xml:space="preserve">millerntor stadion
   hamburg </t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="E33" t="n">
         <v>29546</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>WrbkcjCd</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>S0hPB9rA</t>
         </is>
       </c>
-      <c r="H25" t="n">
-        <v>59</v>
-      </c>
-      <c r="I25" t="n">
-        <v>593</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr">
+      <c r="H33" t="n">
+        <v>59</v>
+      </c>
+      <c r="I33" t="n">
+        <v>593</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
         <is>
           <t>8vndvXTk</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t>pzHxyrtm</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n">
+      <c r="B34" s="2" t="n">
         <v>45522.54166666666</v>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
         <is>
           <t xml:space="preserve">stadion am lotter kreuz
   lotte </t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="E34" t="n">
         <v>10059</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>hjNlCFPB</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>EB3q7jbk</t>
         </is>
       </c>
-      <c r="H26" t="n">
-        <v>59</v>
-      </c>
-      <c r="I26" t="n">
-        <v>593</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
+      <c r="H34" t="n">
+        <v>59</v>
+      </c>
+      <c r="I34" t="n">
+        <v>593</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
         <is>
           <t>naWckLmC</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
         <is>
           <t>dCPKovw8</t>
         </is>
       </c>
-      <c r="B27" s="2" t="n">
+      <c r="B35" s="2" t="n">
         <v>45522.54166666666</v>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
         <is>
           <t xml:space="preserve">hansch arena
   meppen </t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E35" t="n">
         <v>13696</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>rXqBh2xP</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>v9k3aY5F</t>
         </is>
       </c>
-      <c r="H27" t="n">
-        <v>59</v>
-      </c>
-      <c r="I27" t="n">
-        <v>593</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr">
+      <c r="H35" t="n">
+        <v>59</v>
+      </c>
+      <c r="I35" t="n">
+        <v>593</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
         <is>
           <t>ILyJuN3g</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t>vXAKoaf5</t>
         </is>
       </c>
-      <c r="B28" s="2" t="n">
+      <c r="B36" s="2" t="n">
         <v>45522.54166666666</v>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
         <is>
           <t xml:space="preserve">rudolf harbig stadion
   dresden </t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="E36" t="n">
         <v>32249</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>zL1YsOi1</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>ne1oL3y7</t>
         </is>
       </c>
-      <c r="H28" t="n">
-        <v>59</v>
-      </c>
-      <c r="I28" t="n">
-        <v>593</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
+      <c r="H36" t="n">
+        <v>59</v>
+      </c>
+      <c r="I36" t="n">
+        <v>593</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
         <is>
           <t>WG9pOTse</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
         <is>
           <t>06NAdG8N</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n">
+      <c r="B37" s="2" t="n">
         <v>45523.54166666666</v>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
         <is>
           <t xml:space="preserve">stadion der freundschaft
   cottbus </t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="E37" t="n">
         <v>22450</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>6g44VD52</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Ig1f1fy3</t>
         </is>
       </c>
-      <c r="H29" t="n">
-        <v>59</v>
-      </c>
-      <c r="I29" t="n">
-        <v>593</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr">
+      <c r="H37" t="n">
+        <v>59</v>
+      </c>
+      <c r="I37" t="n">
+        <v>593</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
         <is>
           <t>v9k3aY5F</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
         <is>
           <t>Sff03OL7</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n">
+      <c r="B38" s="2" t="n">
         <v>45523.54166666666</v>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
         <is>
           <t xml:space="preserve">bieberer berg stadion
   offenbach am main </t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="E38" t="n">
         <v>20500</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>YJURlaIO</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>YFuz2RLm</t>
         </is>
       </c>
-      <c r="H30" t="n">
-        <v>59</v>
-      </c>
-      <c r="I30" t="n">
-        <v>593</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="H38" t="n">
+        <v>59</v>
+      </c>
+      <c r="I38" t="n">
+        <v>593</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
         <is>
           <t>EkP2bxvB</t>
         </is>
       </c>
-      <c r="B31" s="2" t="n">
+      <c r="B39" s="2" t="n">
         <v>45523.54166666666</v>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
         <is>
           <t xml:space="preserve">stadion oberwerth
   koblenz </t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="E39" t="n">
         <v>9500</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>p8wBsqZt</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>nwkTahLL</t>
         </is>
       </c>
-      <c r="H31" t="n">
-        <v>59</v>
-      </c>
-      <c r="I31" t="n">
-        <v>593</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr">
+      <c r="H39" t="n">
+        <v>59</v>
+      </c>
+      <c r="I39" t="n">
+        <v>593</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
         <is>
           <t>dfNCCCzS</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
         <is>
           <t>pAXo2Kvn</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n">
+      <c r="B40" s="2" t="n">
         <v>45523.65625</v>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
         <is>
           <t xml:space="preserve">eintracht stadion
   braunschweig </t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="E40" t="n">
         <v>23325</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>QqLCC3il</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>8vndvXTk</t>
         </is>
       </c>
-      <c r="H32" t="n">
-        <v>59</v>
-      </c>
-      <c r="I32" t="n">
-        <v>593</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
+      <c r="H40" t="n">
+        <v>59</v>
+      </c>
+      <c r="I40" t="n">
+        <v>593</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>dfNCCCzS</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>EuakNmc1</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
         <is>
           <t>fcxqFy2l</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n">
+      <c r="B41" s="2" t="n">
         <v>45521.64583333334</v>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
         <is>
           <t xml:space="preserve">bayarena
   leverkusen </t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="E41" t="n">
         <v>30210</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>4jcj2zMd</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>nJQmYp1B</t>
         </is>
       </c>
-      <c r="H33" t="n">
-        <v>59</v>
-      </c>
-      <c r="I33" t="n">
+      <c r="H41" t="n">
+        <v>59</v>
+      </c>
+      <c r="I41" t="n">
         <v>594</v>
       </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
         <v>2024</v>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t>super cup</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>WG9pOTse</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>fiEQZ7C7</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1049,25 +1049,25 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45534.64583333334</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">leuna chemie stadion
-  halle </t>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>15057</v>
+        <v>22012</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>boX3cIQa</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1079,10 +1079,10 @@
         <v>59</v>
       </c>
       <c r="I11" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>20242025</v>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1107,40 +1107,40 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45535.4375</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">brita arena
-  wiesbaden </t>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>12566</v>
+        <v>26000</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ObxFt3lm</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="H12" t="n">
         <v>59</v>
       </c>
       <c r="I12" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>20242025</v>
@@ -1152,42 +1152,42 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>0Ija0Ej9</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>WG9pOTse</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45535.4375</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">flyeralarm arena
-  wurzburger </t>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13090</v>
+        <v>58000</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>nVM1YUFj</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1199,10 +1199,10 @@
         <v>59</v>
       </c>
       <c r="I13" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>20242025</v>
@@ -1214,10 +1214,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
           <t>nJQmYp1B</t>
@@ -1227,40 +1231,40 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45520.65625</v>
+        <v>45535.4375</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">donaustadion
-  ulm </t>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>19500</v>
+        <v>15034</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>tbC3EcQn</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>59</v>
       </c>
       <c r="I14" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>20242025</v>
@@ -1272,49 +1276,57 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45521.33333333334</v>
+        <v>45535.4375</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">erzgebirgsstadion
-  aue </t>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>16485</v>
+        <v>60449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>vsXIDreP</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="H15" t="n">
         <v>59</v>
       </c>
       <c r="I15" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>20242025</v>
@@ -1326,53 +1338,57 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45521.33333333334</v>
+        <v>45535.4375</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">bruchwegstadion
-  mainz </t>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7134</v>
+        <v>42100</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>WzEYqEyg</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CCQGbik8</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="H16" t="n">
         <v>59</v>
       </c>
       <c r="I16" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>20242025</v>
@@ -1384,53 +1400,57 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>6FDqshzF</t>
+          <t>0Ija0Ej9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45535.5625</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ostalb arena
-  aalen </t>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>14500</v>
+        <v>30210</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oh2C15j0</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="H17" t="n">
         <v>59</v>
       </c>
       <c r="I17" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>20242025</v>
@@ -1442,10 +1462,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
           <t>nP1i5US1</t>
@@ -1455,40 +1479,40 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45536.4375</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">volksstadion greifswald
-  greifswald </t>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4990</v>
+        <v>15000</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Q1yNyI5t</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="H18" t="n">
         <v>59</v>
       </c>
       <c r="I18" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>20242025</v>
@@ -1500,7 +1524,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1509,40 +1533,40 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45536.52083333334</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">audi sportpark
-  ingolstadt </t>
+          <t xml:space="preserve">allianz arena
+  munich </t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>15800</v>
+        <v>75024</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ne5QkLtB</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>naWckLmC</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="H19" t="n">
         <v>59</v>
       </c>
       <c r="I19" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>20242025</v>
@@ -1554,39 +1578,48 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>06NAdG8N</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45521.4375</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
+        <v>45523.54166666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">osmers h 
+  ger </t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion an der hafenstrasse
-  essen </t>
+          <t xml:space="preserve">stadion der freundschaft
+  cottbus </t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>20352</v>
+        <v>22450</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>EB0xsr77</t>
+          <t>6g44VD52</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1614,37 +1647,42 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>v9k3aY5F</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>Sff03OL7</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45521.4375</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
+        <v>45523.54166666666</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alt p 
+  ger </t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion an der bremer bruck
-  osnabruck </t>
+          <t xml:space="preserve">bieberer berg stadion
+  offenbach am main </t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>16667</v>
+        <v>20500</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>88Xgj1Y5</t>
+          <t>YJURlaIO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>YFuz2RLm</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1670,39 +1708,40 @@
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>EkP2bxvB</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45521.4375</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
+        <v>45523.54166666666</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">storks s 
+  ger </t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ms technologie arena
-  villingen schwenningen </t>
+          <t xml:space="preserve">stadion oberwerth
+  koblenz </t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>8000</v>
+        <v>9500</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>lKLJUxeT</t>
+          <t>p8wBsqZt</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1728,35 +1767,44 @@
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>pAXo2Kvn</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45521.54166666666</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
+        <v>45523.65625</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exner f 
+  ger </t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">new tivoli
-  aachen </t>
+          <t xml:space="preserve">eintracht stadion
+  braunschweig </t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>31026</v>
+        <v>23325</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>j3PKcB4E</t>
+          <t>QqLCC3il</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1781,40 +1829,44 @@
           <t>dfb pokal</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>W67CmLPh</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45531.65625</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">schuco arena
-  bielefeld </t>
+          <t xml:space="preserve">preussenstadion
+  munster </t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>27332</v>
+        <v>12794</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>pp38UXK8</t>
+          <t>zedZaSL7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>dfNCCCzS</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1842,37 +1894,37 @@
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>QqLCC3il</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>6u6i5pie</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45532.54166666666</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion lohmuhle
-  lubeck </t>
+          <t xml:space="preserve">ernst abbe sportfeld
+  jena </t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>17849</v>
+        <v>10445</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>I1Vk6k3R</t>
+          <t>APNl8MIn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1900,927 +1952,7 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>6q2yrHgU</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>45522.33333333334</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ludwigspark stadion
-  saarbrucken </t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>16003</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>fLbhmJ5l</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>6FDqshzF</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>59</v>
-      </c>
-      <c r="I26" t="n">
-        <v>593</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>CCQGbik8</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>AiJ3kset</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>45522.33333333334</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">friedrich ludwig jahn sportpark
-  berlin </t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>19708</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>UNr2EUfd</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>59</v>
-      </c>
-      <c r="I27" t="n">
-        <v>593</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YV3TqwPH</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>45522.4375</v>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadion am panzenberg
-  bremen </t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>tW75B1ei</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>G2Op923t</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>59</v>
-      </c>
-      <c r="I28" t="n">
-        <v>593</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>l0ueP5rR</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>45522.4375</v>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ostseestadion
-  rostock </t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>29000</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>KIHmtCkL</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2y0u8Wrq</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>59</v>
-      </c>
-      <c r="I29" t="n">
-        <v>593</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>t2AoZLAa</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>45522.4375</v>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">friedrich ebert stadium
-  hildesheim </t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>E3xs5mIe</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>6in2Eknb</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>59</v>
-      </c>
-      <c r="I30" t="n">
-        <v>593</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>jFMCm08e</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>45522.4375</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jahnstadion regensburg
-  regensburg </t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>15210</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>UiCmEP56</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>59</v>
-      </c>
-      <c r="I31" t="n">
-        <v>593</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>0Ija0Ej9</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>tvOIPExA</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>45522.4375</v>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hardtwaldstadion
-  sandhausen </t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>15414</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>UZxEj1R4</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
           <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>59</v>
-      </c>
-      <c r="I32" t="n">
-        <v>593</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>KSwfVwAO</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>45522.4375</v>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">millerntor stadion
-  hamburg </t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>29546</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>WrbkcjCd</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>S0hPB9rA</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>59</v>
-      </c>
-      <c r="I33" t="n">
-        <v>593</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>pzHxyrtm</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>45522.54166666666</v>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadion am lotter kreuz
-  lotte </t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>10059</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>hjNlCFPB</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>EB3q7jbk</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>59</v>
-      </c>
-      <c r="I34" t="n">
-        <v>593</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>naWckLmC</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>dCPKovw8</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>45522.54166666666</v>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hansch arena
-  meppen </t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>13696</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>rXqBh2xP</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>59</v>
-      </c>
-      <c r="I35" t="n">
-        <v>593</v>
-      </c>
-      <c r="J35" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>vXAKoaf5</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>45522.54166666666</v>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rudolf harbig stadion
-  dresden </t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>32249</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>zL1YsOi1</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>ne1oL3y7</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>59</v>
-      </c>
-      <c r="I36" t="n">
-        <v>593</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>06NAdG8N</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>45523.54166666666</v>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadion der freundschaft
-  cottbus </t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>22450</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>6g44VD52</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>59</v>
-      </c>
-      <c r="I37" t="n">
-        <v>593</v>
-      </c>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Sff03OL7</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>45523.54166666666</v>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bieberer berg stadion
-  offenbach am main </t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>20500</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>YJURlaIO</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>YFuz2RLm</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>59</v>
-      </c>
-      <c r="I38" t="n">
-        <v>593</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EkP2bxvB</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>45523.54166666666</v>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadion oberwerth
-  koblenz </t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>9500</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>p8wBsqZt</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>59</v>
-      </c>
-      <c r="I39" t="n">
-        <v>593</v>
-      </c>
-      <c r="J39" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>pAXo2Kvn</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>45523.65625</v>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eintracht stadion
-  braunschweig </t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>23325</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>QqLCC3il</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>59</v>
-      </c>
-      <c r="I40" t="n">
-        <v>593</v>
-      </c>
-      <c r="J40" t="n">
-        <v>1</v>
-      </c>
-      <c r="K40" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>fcxqFy2l</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>45521.64583333334</v>
-      </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bayarena
-  leverkusen </t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>30210</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>59</v>
-      </c>
-      <c r="I41" t="n">
-        <v>594</v>
-      </c>
-      <c r="J41" t="n">
-        <v>1</v>
-      </c>
-      <c r="K41" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>super cup</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1049,25 +1049,25 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45534.64583333334</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">leuna chemie stadion
-  halle </t>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>15057</v>
+        <v>22012</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>boX3cIQa</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1079,10 +1079,10 @@
         <v>59</v>
       </c>
       <c r="I11" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>20242025</v>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1107,40 +1107,40 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45535.4375</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">brita arena
-  wiesbaden </t>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>12566</v>
+        <v>26000</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ObxFt3lm</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="H12" t="n">
         <v>59</v>
       </c>
       <c r="I12" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>20242025</v>
@@ -1152,42 +1152,42 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>0Ija0Ej9</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>WG9pOTse</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45535.4375</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">flyeralarm arena
-  wurzburger </t>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13090</v>
+        <v>58000</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>nVM1YUFj</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1199,10 +1199,10 @@
         <v>59</v>
       </c>
       <c r="I13" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>20242025</v>
@@ -1214,10 +1214,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
           <t>nJQmYp1B</t>
@@ -1227,40 +1231,40 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45520.65625</v>
+        <v>45535.4375</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">donaustadion
-  ulm </t>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>19500</v>
+        <v>15034</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>tbC3EcQn</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>59</v>
       </c>
       <c r="I14" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>20242025</v>
@@ -1272,49 +1276,57 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45521.33333333334</v>
+        <v>45535.4375</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">erzgebirgsstadion
-  aue </t>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>16485</v>
+        <v>60449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>vsXIDreP</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="H15" t="n">
         <v>59</v>
       </c>
       <c r="I15" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>20242025</v>
@@ -1326,53 +1338,57 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45521.33333333334</v>
+        <v>45535.4375</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">bruchwegstadion
-  mainz </t>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7134</v>
+        <v>42100</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>WzEYqEyg</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CCQGbik8</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="H16" t="n">
         <v>59</v>
       </c>
       <c r="I16" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>20242025</v>
@@ -1384,53 +1400,57 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>6FDqshzF</t>
+          <t>0Ija0Ej9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45535.5625</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ostalb arena
-  aalen </t>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>14500</v>
+        <v>30210</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oh2C15j0</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="H17" t="n">
         <v>59</v>
       </c>
       <c r="I17" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>20242025</v>
@@ -1442,10 +1462,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
           <t>nP1i5US1</t>
@@ -1455,40 +1479,40 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45536.4375</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">volksstadion greifswald
-  greifswald </t>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4990</v>
+        <v>15000</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Q1yNyI5t</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="H18" t="n">
         <v>59</v>
       </c>
       <c r="I18" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>20242025</v>
@@ -1500,7 +1524,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1509,40 +1533,40 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45536.52083333334</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">audi sportpark
-  ingolstadt </t>
+          <t xml:space="preserve">allianz arena
+  munich </t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>15800</v>
+        <v>75024</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ne5QkLtB</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>naWckLmC</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="H19" t="n">
         <v>59</v>
       </c>
       <c r="I19" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>20242025</v>
@@ -1554,39 +1578,43 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>W67CmLPh</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45531.65625</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion an der hafenstrasse
-  essen </t>
+          <t xml:space="preserve">preussenstadion
+  munster </t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>20352</v>
+        <v>12794</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>EB0xsr77</t>
+          <t>zedZaSL7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1614,37 +1642,37 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>6u6i5pie</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45532.54166666666</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion an der bremer bruck
-  osnabruck </t>
+          <t xml:space="preserve">ernst abbe sportfeld
+  jena </t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>16667</v>
+        <v>10445</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>88Xgj1Y5</t>
+          <t>APNl8MIn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1672,1155 +1700,7 @@
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>8QPARz8c</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>45521.4375</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ms technologie arena
-  villingen schwenningen </t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>8000</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>lKLJUxeT</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>59</v>
-      </c>
-      <c r="I22" t="n">
-        <v>593</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>hzyf0b9b</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>45521.54166666666</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">new tivoli
-  aachen </t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>31026</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>j3PKcB4E</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>63WsD2ei</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>59</v>
-      </c>
-      <c r="I23" t="n">
-        <v>593</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>CpiTEcOi</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>45521.54166666666</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">schuco arena
-  bielefeld </t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>27332</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>pp38UXK8</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>59</v>
-      </c>
-      <c r="I24" t="n">
-        <v>593</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>QqLCC3il</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>8CpxDyg4</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>45521.54166666666</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadion lohmuhle
-  lubeck </t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>17849</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>I1Vk6k3R</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>59</v>
-      </c>
-      <c r="I25" t="n">
-        <v>593</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>0Ija0Ej9</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>6q2yrHgU</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>45522.33333333334</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ludwigspark stadion
-  saarbrucken </t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>16003</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>fLbhmJ5l</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>6FDqshzF</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>59</v>
-      </c>
-      <c r="I26" t="n">
-        <v>593</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>CCQGbik8</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>AiJ3kset</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>45522.33333333334</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">friedrich ludwig jahn sportpark
-  berlin </t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>19708</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>UNr2EUfd</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>59</v>
-      </c>
-      <c r="I27" t="n">
-        <v>593</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YV3TqwPH</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>45522.4375</v>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadion am panzenberg
-  bremen </t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>tW75B1ei</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>G2Op923t</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>59</v>
-      </c>
-      <c r="I28" t="n">
-        <v>593</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>l0ueP5rR</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>45522.4375</v>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ostseestadion
-  rostock </t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>29000</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>KIHmtCkL</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2y0u8Wrq</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>59</v>
-      </c>
-      <c r="I29" t="n">
-        <v>593</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>t2AoZLAa</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>45522.4375</v>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">friedrich ebert stadium
-  hildesheim </t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>E3xs5mIe</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>6in2Eknb</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>59</v>
-      </c>
-      <c r="I30" t="n">
-        <v>593</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>jFMCm08e</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>45522.4375</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jahnstadion regensburg
-  regensburg </t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>15210</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>UiCmEP56</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>59</v>
-      </c>
-      <c r="I31" t="n">
-        <v>593</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>0Ija0Ej9</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>tvOIPExA</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>45522.4375</v>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hardtwaldstadion
-  sandhausen </t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>15414</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>UZxEj1R4</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
           <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>59</v>
-      </c>
-      <c r="I32" t="n">
-        <v>593</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>KSwfVwAO</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>45522.4375</v>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">millerntor stadion
-  hamburg </t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>29546</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>WrbkcjCd</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>S0hPB9rA</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>59</v>
-      </c>
-      <c r="I33" t="n">
-        <v>593</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>pzHxyrtm</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>45522.54166666666</v>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadion am lotter kreuz
-  lotte </t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>10059</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>hjNlCFPB</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>EB3q7jbk</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>59</v>
-      </c>
-      <c r="I34" t="n">
-        <v>593</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>naWckLmC</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>dCPKovw8</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>45522.54166666666</v>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hansch arena
-  meppen </t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>13696</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>rXqBh2xP</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>59</v>
-      </c>
-      <c r="I35" t="n">
-        <v>593</v>
-      </c>
-      <c r="J35" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>vXAKoaf5</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>45522.54166666666</v>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rudolf harbig stadion
-  dresden </t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>32249</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>zL1YsOi1</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>ne1oL3y7</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>59</v>
-      </c>
-      <c r="I36" t="n">
-        <v>593</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>06NAdG8N</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>45523.54166666666</v>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadion der freundschaft
-  cottbus </t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>22450</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>6g44VD52</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>59</v>
-      </c>
-      <c r="I37" t="n">
-        <v>593</v>
-      </c>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Sff03OL7</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>45523.54166666666</v>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bieberer berg stadion
-  offenbach am main </t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>20500</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>YJURlaIO</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>YFuz2RLm</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>59</v>
-      </c>
-      <c r="I38" t="n">
-        <v>593</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EkP2bxvB</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>45523.54166666666</v>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadion oberwerth
-  koblenz </t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>9500</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>p8wBsqZt</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>59</v>
-      </c>
-      <c r="I39" t="n">
-        <v>593</v>
-      </c>
-      <c r="J39" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>pAXo2Kvn</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>45523.65625</v>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eintracht stadion
-  braunschweig </t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>23325</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>QqLCC3il</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>59</v>
-      </c>
-      <c r="I40" t="n">
-        <v>593</v>
-      </c>
-      <c r="J40" t="n">
-        <v>1</v>
-      </c>
-      <c r="K40" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>fcxqFy2l</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>45521.64583333334</v>
-      </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bayarena
-  leverkusen </t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>30210</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>59</v>
-      </c>
-      <c r="I41" t="n">
-        <v>594</v>
-      </c>
-      <c r="J41" t="n">
-        <v>1</v>
-      </c>
-      <c r="K41" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>super cup</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,6 +503,41 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -565,6 +600,27 @@
           <t>WG9pOTse</t>
         </is>
       </c>
+      <c r="P2" t="n">
+        <v>20.33333333333333</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>199</v>
+      </c>
+      <c r="U2" t="n">
+        <v>8225000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>231</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -623,6 +679,13 @@
           <t>v9k3aY5F</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -685,6 +748,13 @@
           <t>fiEQZ7C7</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -747,6 +817,13 @@
           <t>ILyJuN3g</t>
         </is>
       </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -805,6 +882,13 @@
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -867,6 +951,13 @@
           <t>0Ija0Ej9</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -929,6 +1020,13 @@
           <t>EuakNmc1</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -987,6 +1085,13 @@
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1045,6 +1150,13 @@
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1103,6 +1215,13 @@
           <t>v9k3aY5F</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1165,6 +1284,13 @@
           <t>WG9pOTse</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1227,6 +1353,13 @@
           <t>nJQmYp1B</t>
         </is>
       </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1289,6 +1422,13 @@
           <t>dfNCCCzS</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1351,6 +1491,13 @@
           <t>8vndvXTk</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1413,6 +1560,13 @@
           <t>0Ija0Ej9</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1475,6 +1629,13 @@
           <t>nP1i5US1</t>
         </is>
       </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1529,6 +1690,13 @@
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1587,122 +1755,13 @@
           <t>nJQmYp1B</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>W67CmLPh</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">preussenstadion
-  munster </t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>12794</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>zedZaSL7</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>59</v>
-      </c>
-      <c r="I20" t="n">
-        <v>593</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>6u6i5pie</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45532.54166666666</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ernst abbe sportfeld
-  jena </t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>10445</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>APNl8MIn</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>59</v>
-      </c>
-      <c r="I21" t="n">
-        <v>593</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,35 +577,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
+          <t>t0w6KHuf</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45529.4375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stegemann s 
+          <t xml:space="preserve">siebert d 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">wwk arena
-  augsburg </t>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>30660</v>
+        <v>28917</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -630,87 +630,87 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>25.66666666666667</v>
+        <v>22</v>
       </c>
       <c r="Q2" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>214</v>
+        <v>149</v>
       </c>
       <c r="U2" t="n">
-        <v>9400000</v>
+        <v>21000000</v>
       </c>
       <c r="V2" t="n">
-        <v>220</v>
+        <v>164</v>
       </c>
       <c r="W2" t="n">
-        <v>26.5</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="X2" t="n">
-        <v>182</v>
+        <v>184.8333333333333</v>
       </c>
       <c r="Y2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AA2" t="n">
-        <v>150</v>
+        <v>430</v>
       </c>
       <c r="AB2" t="n">
-        <v>13000000</v>
+        <v>98525000</v>
       </c>
       <c r="AC2" t="n">
-        <v>154</v>
+        <v>489</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
+          <t>AuVMGZvJ</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45529.52083333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">jablonski s 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">europa park stadion
-  freiburg </t>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>34700</v>
+        <v>29546</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -737,89 +737,66 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>23.83333333333333</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>186.3333333333333</v>
-      </c>
-      <c r="R3" t="n">
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>23</v>
+      </c>
+      <c r="X3" t="n">
+        <v>186</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1</v>
       </c>
-      <c r="S3" t="n">
-        <v>6</v>
-      </c>
-      <c r="T3" t="n">
-        <v>428</v>
-      </c>
-      <c r="U3" t="n">
-        <v>24500000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>457</v>
-      </c>
-      <c r="W3" t="n">
-        <v>22.28571428571428</v>
-      </c>
-      <c r="X3" t="n">
-        <v>188.7142857142857</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.285714285714286</v>
-      </c>
       <c r="Z3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>495</v>
+        <v>66</v>
       </c>
       <c r="AB3" t="n">
-        <v>36825000</v>
+        <v>1100000</v>
       </c>
       <c r="AC3" t="n">
-        <v>541</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.4375</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stieler t 
-  ger </t>
-        </is>
-      </c>
+        <v>45534.64583333334</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">prezero arena
-  sinsheim </t>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>30150</v>
+        <v>22012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -844,91 +821,54 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>23.42857142857143</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>182.7142857142857</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.428571428571429</v>
-      </c>
-      <c r="S4" t="n">
-        <v>7</v>
-      </c>
-      <c r="T4" t="n">
-        <v>512</v>
-      </c>
-      <c r="U4" t="n">
-        <v>48000000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>558</v>
-      </c>
-      <c r="W4" t="n">
-        <v>26.33333333333333</v>
-      </c>
-      <c r="X4" t="n">
-        <v>184</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>207</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>5750000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>217</v>
-      </c>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45528.4375</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">osmers h 
-  ger </t>
-        </is>
-      </c>
+        <v>45535.4375</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">mewa arena
-  mainz </t>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>34000</v>
+        <v>26000</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -955,10 +895,14 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -966,60 +910,41 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>29</v>
-      </c>
-      <c r="X5" t="n">
-        <v>175.6666666666667</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>229</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>25300000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>229</v>
-      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45528.4375</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brand b 
-  ger </t>
-        </is>
-      </c>
+        <v>45535.4375</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">red bull arena
-  leipzig </t>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>47069</v>
+        <v>58000</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1046,89 +971,56 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>185.75</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>294</v>
-      </c>
-      <c r="U6" t="n">
-        <v>66900000</v>
-      </c>
-      <c r="V6" t="n">
-        <v>336</v>
-      </c>
-      <c r="W6" t="n">
-        <v>27.33333333333333</v>
-      </c>
-      <c r="X6" t="n">
-        <v>188.6666666666667</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>213</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>6550000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>224</v>
-      </c>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SxFxJ44k</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45528.5625</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zwayer f 
-  ger </t>
-        </is>
-      </c>
+        <v>45535.4375</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">signal iduna park
-  dortmund </t>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>81365</v>
+        <v>15034</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1155,56 +1047,396 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>61DvZGfm</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45535.4375</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>60449</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>59</v>
+      </c>
+      <c r="I8" t="n">
+        <v>591</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>0OYDmG9t</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45535.4375</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>42100</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>59</v>
+      </c>
+      <c r="I9" t="n">
+        <v>591</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>0Ija0Ej9</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>143</v>
-      </c>
-      <c r="U7" t="n">
-        <v>29000000</v>
-      </c>
-      <c r="V7" t="n">
-        <v>161</v>
-      </c>
-      <c r="W7" t="n">
-        <v>19</v>
-      </c>
-      <c r="X7" t="n">
-        <v>180</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>121</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1575000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>159</v>
-      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AVR8vwXP</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45535.5625</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I10" t="n">
+        <v>591</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>W8b4TCOO</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45536.4375</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>59</v>
+      </c>
+      <c r="I11" t="n">
+        <v>591</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2T6mXfPa</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45536.52083333334</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz arena
+  munich </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>75024</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>59</v>
+      </c>
+      <c r="I12" t="n">
+        <v>591</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,109 +503,34 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_home</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_home</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_home</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_home</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_home</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_home</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_home</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_away</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>t0w6KHuf</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45529.4375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">siebert d 
-  ger </t>
-        </is>
-      </c>
+        <v>45534.64583333334</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">volkswagen arena
-  wolfsburg </t>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>28917</v>
+        <v>22012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -630,87 +555,40 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>180</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>149</v>
-      </c>
-      <c r="U2" t="n">
-        <v>21000000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>164</v>
-      </c>
-      <c r="W2" t="n">
-        <v>21.83333333333333</v>
-      </c>
-      <c r="X2" t="n">
-        <v>184.8333333333333</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>430</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>98525000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>489</v>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>AuVMGZvJ</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45529.52083333334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jablonski s 
-  ger </t>
-        </is>
-      </c>
+        <v>45535.4375</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">millerntor stadion
-  hamburg </t>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>29546</v>
+        <v>26000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -737,66 +615,42 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="n">
-        <v>23</v>
-      </c>
-      <c r="X3" t="n">
-        <v>186</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>66</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>70</v>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>djSMofvg</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45534.64583333334</v>
+        <v>45535.4375</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion an der alten forsterei
-  berlin </t>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>22012</v>
+        <v>58000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -821,31 +675,21 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>U3QUqY85</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -854,21 +698,21 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">vonovia ruhrstadion
-  bochum </t>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>26000</v>
+        <v>15034</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -895,33 +739,19 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>AgAeVYgC</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -930,21 +760,21 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">deutsche bank park
-  frankfurt </t>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>58000</v>
+        <v>60449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -971,33 +801,19 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>QVJwrCwI</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1006,21 +822,21 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">holstein stadion
-  kiel </t>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15034</v>
+        <v>42100</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1047,56 +863,42 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>v9k3aY5F</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>61DvZGfm</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45535.4375</v>
+        <v>45535.5625</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mhparena
-  stuttgart </t>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>60449</v>
+        <v>30210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1123,56 +925,42 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>WG9pOTse</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>0OYDmG9t</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45535.4375</v>
+        <v>45536.4375</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">weserstadion
-  bremen </t>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>42100</v>
+        <v>15000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1197,58 +985,36 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0Ija0Ej9</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>AVR8vwXP</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.52083333334</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">bayarena
-  leverkusen </t>
+          <t xml:space="preserve">allianz arena
+  munich </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>30210</v>
+        <v>75024</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1273,170 +1039,12 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>W8b4TCOO</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45536.4375</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">voith arena
-  heidenheim </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>59</v>
-      </c>
-      <c r="I11" t="n">
-        <v>591</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2T6mXfPa</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45536.52083333334</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allianz arena
-  munich </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>75024</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>nVp0wiqd</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>59</v>
-      </c>
-      <c r="I12" t="n">
-        <v>591</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
-        <is>
           <t>nJQmYp1B</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,6 +503,76 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -561,6 +631,48 @@
           <t>v9k3aY5F</t>
         </is>
       </c>
+      <c r="P2" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>175.6666666666667</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>229</v>
+      </c>
+      <c r="U2" t="n">
+        <v>25300000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>229</v>
+      </c>
+      <c r="W2" t="n">
+        <v>30</v>
+      </c>
+      <c r="X2" t="n">
+        <v>186.6666666666667</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>199</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2575000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>204</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -623,6 +735,20 @@
           <t>WG9pOTse</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -685,6 +811,20 @@
           <t>nJQmYp1B</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -747,6 +887,20 @@
           <t>dfNCCCzS</t>
         </is>
       </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -809,6 +963,20 @@
           <t>8vndvXTk</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -871,6 +1039,20 @@
           <t>0Ija0Ej9</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -933,6 +1115,20 @@
           <t>nP1i5US1</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -987,6 +1183,20 @@
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1045,6 +1255,20 @@
           <t>nJQmYp1B</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,30 +577,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>djSMofvg</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45534.64583333334</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>45535.4375</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">storks s 
+  ger </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion an der alten forsterei
-  berlin </t>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>22012</v>
+        <v>26000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -625,38 +630,42 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>v9k3aY5F</t>
+          <t>WG9pOTse</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>29</v>
+        <v>27.33333333333333</v>
       </c>
       <c r="Q2" t="n">
-        <v>175.6666666666667</v>
+        <v>188.6666666666667</v>
       </c>
       <c r="R2" t="n">
-        <v>1.666666666666667</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="U2" t="n">
-        <v>25300000</v>
+        <v>6550000</v>
       </c>
       <c r="V2" t="n">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="W2" t="n">
-        <v>30</v>
+        <v>19.33333333333333</v>
       </c>
       <c r="X2" t="n">
-        <v>186.6666666666667</v>
+        <v>181.3333333333333</v>
       </c>
       <c r="Y2" t="n">
         <v>1</v>
@@ -665,42 +674,47 @@
         <v>3</v>
       </c>
       <c r="AA2" t="n">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="AB2" t="n">
-        <v>2575000</v>
+        <v>4625000</v>
       </c>
       <c r="AC2" t="n">
-        <v>204</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U3QUqY85</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
         <v>45535.4375</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badstubner f 
+  ger </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">vonovia ruhrstadion
-  bochum </t>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>26000</v>
+        <v>58000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -727,56 +741,89 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>180</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" t="n">
+        <v>121</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>159</v>
+      </c>
+      <c r="W3" t="n">
+        <v>23</v>
+      </c>
+      <c r="X3" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>362</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>25600000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>399</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AgAeVYgC</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>45535.4375</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exner f 
+  ger </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">deutsche bank park
-  frankfurt </t>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>58000</v>
+        <v>15034</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -803,56 +850,89 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>140</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>149</v>
+      </c>
+      <c r="W4" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="X4" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>226</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>33000000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>243</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>QVJwrCwI</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
         <v>45535.4375</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gerach t 
+  ger </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">holstein stadion
-  kiel </t>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>15034</v>
+        <v>60449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -879,56 +959,89 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>187</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>351</v>
+      </c>
+      <c r="U5" t="n">
+        <v>27625000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>392</v>
+      </c>
+      <c r="W5" t="n">
+        <v>24</v>
+      </c>
+      <c r="X5" t="n">
+        <v>190</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>61DvZGfm</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>45535.4375</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">mhparena
-  stuttgart </t>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>60449</v>
+        <v>42100</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -955,21 +1068,35 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>v9k3aY5F</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>182</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>150</v>
+      </c>
+      <c r="U6" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>154</v>
+      </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
@@ -981,30 +1108,35 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0OYDmG9t</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45535.4375</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>45535.5625</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jollenbeck m 
+  ger </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">weserstadion
-  bremen </t>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>42100</v>
+        <v>30210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1031,56 +1163,84 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>v9k3aY5F</t>
+          <t>WG9pOTse</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>178</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>81</v>
+      </c>
+      <c r="U7" t="n">
+        <v>36500000</v>
+      </c>
+      <c r="V7" t="n">
+        <v>85</v>
+      </c>
+      <c r="W7" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X7" t="n">
+        <v>186.75</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>297</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>63400000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>333</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>AVR8vwXP</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.4375</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">bayarena
-  leverkusen </t>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>30210</v>
+        <v>15000</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1105,58 +1265,78 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>186</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>66</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="V8" t="n">
+        <v>70</v>
+      </c>
+      <c r="W8" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="X8" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>287</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>12800000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>295</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>W8b4TCOO</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45536.4375</v>
+        <v>45536.52083333334</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">voith arena
-  heidenheim </t>
+          <t xml:space="preserve">allianz arena
+  munich </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>15000</v>
+        <v>75024</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1182,49 +1362,81 @@
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>21.83333333333333</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>184.8333333333333</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6</v>
+      </c>
+      <c r="T9" t="n">
+        <v>430</v>
+      </c>
+      <c r="U9" t="n">
+        <v>98525000</v>
+      </c>
+      <c r="V9" t="n">
+        <v>489</v>
+      </c>
+      <c r="W9" t="n">
+        <v>24.71428571428572</v>
+      </c>
+      <c r="X9" t="n">
+        <v>186.5714285714286</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>35900000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>532</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2T6mXfPa</t>
+          <t>zsmd0ggn</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45536.52083333334</v>
+        <v>45548.64583333334</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz arena
-  munich </t>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>75024</v>
+        <v>81365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1249,12 +1461,12 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -1270,6 +1482,454 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UwsvBA74</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>54042</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>59</v>
+      </c>
+      <c r="I11" t="n">
+        <v>591</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>vZqDdBhB</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>34700</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>59</v>
+      </c>
+      <c r="I12" t="n">
+        <v>591</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>r7j4bXNb</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>30150</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>59</v>
+      </c>
+      <c r="I13" t="n">
+        <v>591</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>WSMotj8U</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>47069</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>59</v>
+      </c>
+      <c r="I14" t="n">
+        <v>591</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>tI0qkTpo</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>28917</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>59</v>
+      </c>
+      <c r="I15" t="n">
+        <v>591</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>x4pn9lxH</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45549.5625</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>15034</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>59</v>
+      </c>
+      <c r="I16" t="n">
+        <v>591</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB3"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,107 +495,42 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>id_team_home_rival_team</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>id_team_away_rival_team</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_home</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_home</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_home</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_home</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_home</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_home</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_home</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_away</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_away</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>W8b4TCOO</t>
+          <t>zsmd0ggn</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45536.4375</v>
+        <v>45548.64583333334</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">voith arena
-  heidenheim </t>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>15000</v>
+        <v>81365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -620,77 +555,40 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>23</v>
-      </c>
-      <c r="P2" t="n">
-        <v>186</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>66</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>70</v>
-      </c>
-      <c r="V2" t="n">
-        <v>25.66666666666667</v>
-      </c>
-      <c r="W2" t="n">
-        <v>183</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>214</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>9400000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>220</v>
-      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2T6mXfPa</t>
+          <t>UwsvBA74</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45536.52083333334</v>
+        <v>45549.4375</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz arena
-  munich </t>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>75024</v>
+        <v>54042</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -717,50 +615,435 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>vZqDdBhB</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>34700</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>59</v>
+      </c>
+      <c r="I4" t="n">
+        <v>591</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>nJQmYp1B</t>
         </is>
       </c>
-      <c r="O3" t="n">
-        <v>21.83333333333333</v>
-      </c>
-      <c r="P3" t="n">
-        <v>184.8333333333333</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6</v>
-      </c>
-      <c r="S3" t="n">
-        <v>430</v>
-      </c>
-      <c r="T3" t="n">
-        <v>98525000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>489</v>
-      </c>
-      <c r="V3" t="n">
-        <v>24.77777777777778</v>
-      </c>
-      <c r="W3" t="n">
-        <v>186.3333333333333</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.222222222222222</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>648</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>47100000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>686</v>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>r7j4bXNb</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>30150</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>59</v>
+      </c>
+      <c r="I5" t="n">
+        <v>591</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>WSMotj8U</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>47069</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>59</v>
+      </c>
+      <c r="I6" t="n">
+        <v>591</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>tI0qkTpo</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>28917</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>59</v>
+      </c>
+      <c r="I7" t="n">
+        <v>591</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>x4pn9lxH</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45549.5625</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>15034</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>59</v>
+      </c>
+      <c r="I8" t="n">
+        <v>591</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>CnrLfkNN</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45550.4375</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>30660</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>59</v>
+      </c>
+      <c r="I9" t="n">
+        <v>591</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8OhVCWxh</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45550.52083333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I10" t="n">
+        <v>591</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1046,6 +1046,548 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>dCL13J5e</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45555.64583333334</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>30660</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>59</v>
+      </c>
+      <c r="I11" t="n">
+        <v>591</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pY1dP0SE</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>59</v>
+      </c>
+      <c r="I12" t="n">
+        <v>591</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>QNoNA1DL</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>59</v>
+      </c>
+      <c r="I13" t="n">
+        <v>591</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>hvFA1cz8</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>22012</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>59</v>
+      </c>
+      <c r="I14" t="n">
+        <v>591</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>AeNg5uyq</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>42100</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>59</v>
+      </c>
+      <c r="I15" t="n">
+        <v>591</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>IcrFCNr9</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45556.5625</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>58000</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>59</v>
+      </c>
+      <c r="I16" t="n">
+        <v>591</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Uy2KjtMk</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45557.4375</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>59</v>
+      </c>
+      <c r="I17" t="n">
+        <v>591</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>2k0SlKj2</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45557.52083333334</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>60449</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>59</v>
+      </c>
+      <c r="I18" t="n">
+        <v>591</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dQ0zIIKl</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45557.60416666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>29546</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>59</v>
+      </c>
+      <c r="I19" t="n">
+        <v>591</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,92 +503,17 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_home</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_home</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_home</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_home</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_home</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_home</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_home</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_away</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CnrLfkNN</t>
+          <t>dCL13J5e</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.4375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zwayer f 
-  ger </t>
-        </is>
-      </c>
+        <v>45555.64583333334</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">wwk arena
@@ -605,7 +530,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -633,159 +558,1034 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>25.66666666666667</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>183</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>214</v>
-      </c>
-      <c r="U2" t="n">
-        <v>9400000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>220</v>
-      </c>
-      <c r="W2" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="X2" t="n">
-        <v>187</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>339</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>7075000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>352</v>
+          <t>8vndvXTk</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8OhVCWxh</t>
+          <t>pY1dP0SE</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.52083333334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brand b 
-  ger </t>
-        </is>
-      </c>
+        <v>45556.4375</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>59</v>
+      </c>
+      <c r="I3" t="n">
+        <v>591</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>QNoNA1DL</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>59</v>
+      </c>
+      <c r="I4" t="n">
+        <v>591</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>hvFA1cz8</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>22012</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>59</v>
+      </c>
+      <c r="I5" t="n">
+        <v>591</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>AeNg5uyq</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>42100</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>59</v>
+      </c>
+      <c r="I6" t="n">
+        <v>591</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>IcrFCNr9</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45556.5625</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>58000</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>59</v>
+      </c>
+      <c r="I7" t="n">
+        <v>591</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Uy2KjtMk</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45557.4375</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>59</v>
+      </c>
+      <c r="I8" t="n">
+        <v>591</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>2k0SlKj2</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45557.52083333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>60449</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>59</v>
+      </c>
+      <c r="I9" t="n">
+        <v>591</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>dQ0zIIKl</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45557.60416666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>29546</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I10" t="n">
+        <v>591</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>rsNyMnwK</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45562.64583333334</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>81365</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>59</v>
+      </c>
+      <c r="I11" t="n">
+        <v>591</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CIlrT3pm</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>54042</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>59</v>
+      </c>
+      <c r="I12" t="n">
+        <v>591</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>6uSGCr06</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>34700</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>59</v>
+      </c>
+      <c r="I13" t="n">
+        <v>591</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>f18BYPMP</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t xml:space="preserve">mewa arena
   mainz </t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E14" t="n">
         <v>34000</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>EuakNmc1</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>59</v>
+      </c>
+      <c r="I14" t="n">
+        <v>591</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Q5hiEzKD</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>47069</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>59</v>
+      </c>
+      <c r="I15" t="n">
+        <v>591</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SfGPAMUI</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>28917</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>59</v>
+      </c>
+      <c r="I16" t="n">
+        <v>591</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>IukqGdk1</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45563.5625</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz arena
+  munich </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>75024</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>59</v>
+      </c>
+      <c r="I17" t="n">
+        <v>591</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>pWnjRsFa</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45564.4375</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>15034</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>59</v>
+      </c>
+      <c r="I18" t="n">
+        <v>591</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>bFO8E4Vg</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45564.52083333334</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>30150</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>Ig1f1fy3</t>
         </is>
       </c>
-      <c r="H3" t="n">
-        <v>59</v>
-      </c>
-      <c r="I3" t="n">
-        <v>591</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="H19" t="n">
+        <v>59</v>
+      </c>
+      <c r="I19" t="n">
+        <v>591</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>v9k3aY5F</t>
         </is>
-      </c>
-      <c r="P3" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>185</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>75</v>
-      </c>
-      <c r="U3" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>78</v>
-      </c>
-      <c r="W3" t="n">
-        <v>27</v>
-      </c>
-      <c r="X3" t="n">
-        <v>181.3333333333333</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>217</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>11600000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>217</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,34 +503,109 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>dCL13J5e</t>
+          <t>pY1dP0SE</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45555.64583333334</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>45556.4375</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">petersen m 
+  ger </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">wwk arena
-  augsburg </t>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>30660</v>
+        <v>26000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -555,40 +630,91 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
-        </is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T2" t="n">
+        <v>294</v>
+      </c>
+      <c r="U2" t="n">
+        <v>10200000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>294</v>
+      </c>
+      <c r="W2" t="n">
+        <v>24</v>
+      </c>
+      <c r="X2" t="n">
+        <v>193.5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>137</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>3700000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>146</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pY1dP0SE</t>
+          <t>QNoNA1DL</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
         <v>45556.4375</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brand b 
+  ger </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">vonovia ruhrstadion
-  bochum </t>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>26000</v>
+        <v>15000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -613,44 +739,87 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0Ija0Ej9</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
-        </is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" t="n">
+        <v>125</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>143</v>
+      </c>
+      <c r="W3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="X3" t="n">
+        <v>186.3333333333333</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>434</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>30200000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>447</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>QNoNA1DL</t>
+          <t>hvFA1cz8</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>45556.4375</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jollenbeck m 
+  ger </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">voith arena
-  heidenheim </t>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>15000</v>
+        <v>22012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -680,35 +849,82 @@
         <is>
           <t>nJQmYp1B</t>
         </is>
+      </c>
+      <c r="P4" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>173</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>77</v>
+      </c>
+      <c r="U4" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>77</v>
+      </c>
+      <c r="W4" t="n">
+        <v>26.14285714285714</v>
+      </c>
+      <c r="X4" t="n">
+        <v>183</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.714285714285714</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>529</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>67700000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>548</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hvFA1cz8</t>
+          <t>AeNg5uyq</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
         <v>45556.4375</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dankert b 
+  ger </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion an der alten forsterei
-  berlin </t>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>22012</v>
+        <v>42100</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -733,40 +949,87 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>184.3333333333333</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>213</v>
+      </c>
+      <c r="U5" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>219</v>
+      </c>
+      <c r="W5" t="n">
+        <v>21</v>
+      </c>
+      <c r="X5" t="n">
+        <v>184</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>424</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>56025000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>488</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>AeNg5uyq</t>
+          <t>IcrFCNr9</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45556.4375</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>45556.5625</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">welz t 
+  ger </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">weserstadion
-  bremen </t>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>42100</v>
+        <v>58000</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -793,38 +1056,89 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>285</v>
+      </c>
+      <c r="U6" t="n">
+        <v>40575000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>323</v>
+      </c>
+      <c r="W6" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="X6" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>352</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>36125000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>389</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>IcrFCNr9</t>
+          <t>Uy2KjtMk</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45556.5625</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>45557.4375</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stegemann s 
+  ger </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">deutsche bank park
-  frankfurt </t>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>58000</v>
+        <v>30210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -851,42 +1165,75 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>WG9pOTse</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
-        </is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="X7" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>305</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>57500000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>326</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Uy2KjtMk</t>
+          <t>2k0SlKj2</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45557.4375</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>45557.52083333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badstubner f 
+  ger </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">bayarena
-  leverkusen </t>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>30210</v>
+        <v>60449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -913,42 +1260,89 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>dfNCCCzS</t>
-        </is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>20.66666666666667</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>182</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>205</v>
+      </c>
+      <c r="U8" t="n">
+        <v>9300000</v>
+      </c>
+      <c r="V8" t="n">
+        <v>241</v>
+      </c>
+      <c r="W8" t="n">
+        <v>20</v>
+      </c>
+      <c r="X8" t="n">
+        <v>185</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>78</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2k0SlKj2</t>
+          <t>dQ0zIIKl</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45557.52083333334</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>45557.60416666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">mhparena
-  stuttgart </t>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>60449</v>
+        <v>29546</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -975,617 +1369,55 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>v9k3aY5F</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>dQ0zIIKl</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45557.60416666666</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">millerntor stadion
-  hamburg </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>29546</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>KbS1suSm</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I10" t="n">
-        <v>591</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
           <t>nP1i5US1</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>rsNyMnwK</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45562.64583333334</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">signal iduna park
-  dortmund </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>81365</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>59</v>
-      </c>
-      <c r="I11" t="n">
-        <v>591</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0Ija0Ej9</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0Ija0Ej9</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>CIlrT3pm</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45563.4375</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">borussia park
-  monchengladbach </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>54042</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>pzHW4oaE</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>59</v>
-      </c>
-      <c r="I12" t="n">
-        <v>591</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>6uSGCr06</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45563.4375</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">europa park stadion
-  freiburg </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>34700</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>59</v>
-      </c>
-      <c r="I13" t="n">
-        <v>591</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>f18BYPMP</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45563.4375</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mewa arena
-  mainz </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>34000</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>59</v>
-      </c>
-      <c r="I14" t="n">
-        <v>591</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Q5hiEzKD</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45563.4375</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">red bull arena
-  leipzig </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>47069</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>KbS1suSm</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>59</v>
-      </c>
-      <c r="I15" t="n">
-        <v>591</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>SfGPAMUI</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45563.4375</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">volkswagen arena
-  wolfsburg </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>28917</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>59</v>
-      </c>
-      <c r="I16" t="n">
-        <v>591</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>IukqGdk1</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45563.5625</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allianz arena
-  munich </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>75024</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>nVp0wiqd</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>59</v>
-      </c>
-      <c r="I17" t="n">
-        <v>591</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>pWnjRsFa</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45564.4375</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">holstein stadion
-  kiel </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>15034</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>63WsD2ei</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>59</v>
-      </c>
-      <c r="I18" t="n">
-        <v>591</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>bFO8E4Vg</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45564.52083333334</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prezero arena
-  sinsheim </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>30150</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>hQAtP9Sl</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>59</v>
-      </c>
-      <c r="I19" t="n">
-        <v>591</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
+      <c r="P9" t="n">
+        <v>26.83333333333333</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>186.1666666666667</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6</v>
+      </c>
+      <c r="T9" t="n">
+        <v>410</v>
+      </c>
+      <c r="U9" t="n">
+        <v>10975000</v>
+      </c>
+      <c r="V9" t="n">
+        <v>429</v>
+      </c>
+      <c r="W9" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="X9" t="n">
+        <v>181</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>224</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>41800000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>245</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,289 +503,1089 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_home</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_home</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_home</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_home</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_home</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_home</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_home</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_away</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CnrLfkNN</t>
+          <t>rsNyMnwK</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.4375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zwayer f 
-  ger </t>
-        </is>
-      </c>
+        <v>45562.64583333334</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>81365</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>59</v>
+      </c>
+      <c r="I2" t="n">
+        <v>591</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>CIlrT3pm</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>54042</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>59</v>
+      </c>
+      <c r="I3" t="n">
+        <v>591</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>6uSGCr06</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>34700</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>59</v>
+      </c>
+      <c r="I4" t="n">
+        <v>591</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>f18BYPMP</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>59</v>
+      </c>
+      <c r="I5" t="n">
+        <v>591</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Q5hiEzKD</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>47069</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>59</v>
+      </c>
+      <c r="I6" t="n">
+        <v>591</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SfGPAMUI</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>28917</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>59</v>
+      </c>
+      <c r="I7" t="n">
+        <v>591</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>IukqGdk1</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45563.5625</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz arena
+  munich </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>75024</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>59</v>
+      </c>
+      <c r="I8" t="n">
+        <v>591</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>pWnjRsFa</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45564.4375</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>15034</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>59</v>
+      </c>
+      <c r="I9" t="n">
+        <v>591</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>bFO8E4Vg</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45564.52083333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>30150</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I10" t="n">
+        <v>591</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UajsPCkT</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45569.64583333334</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">wwk arena
   augsburg </t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E11" t="n">
         <v>30660</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>fTVNku3I</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>59</v>
+      </c>
+      <c r="I11" t="n">
+        <v>591</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>tbtaPLqC</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>59</v>
+      </c>
+      <c r="I12" t="n">
+        <v>591</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>ILyJuN3g</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>59</v>
-      </c>
-      <c r="I2" t="n">
-        <v>591</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ENOasf5c</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>59</v>
+      </c>
+      <c r="I13" t="n">
+        <v>591</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>lpXDJjDj</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>22012</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>59</v>
+      </c>
+      <c r="I14" t="n">
+        <v>591</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>dnhZQYKG</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>42100</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>59</v>
+      </c>
+      <c r="I15" t="n">
+        <v>591</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>v9k3aY5F</t>
         </is>
       </c>
-      <c r="P2" t="n">
-        <v>25.66666666666667</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>183</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>214</v>
-      </c>
-      <c r="U2" t="n">
-        <v>9400000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>220</v>
-      </c>
-      <c r="W2" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="X2" t="n">
-        <v>187</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>339</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>7075000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>8OhVCWxh</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45550.52083333334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brand b 
-  ger </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mewa arena
-  mainz </t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>34000</v>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>zwD8uYZ9</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45570.5625</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>29546</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>EuakNmc1</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>59</v>
-      </c>
-      <c r="I3" t="n">
-        <v>591</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="H16" t="n">
+        <v>59</v>
+      </c>
+      <c r="I16" t="n">
+        <v>591</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>8vndvXTk</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>185</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>75</v>
-      </c>
-      <c r="U3" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>78</v>
-      </c>
-      <c r="W3" t="n">
-        <v>27</v>
-      </c>
-      <c r="X3" t="n">
-        <v>181.3333333333333</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>217</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>11600000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>217</v>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>0KbQSfj4</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45571.4375</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>59</v>
+      </c>
+      <c r="I17" t="n">
+        <v>591</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ShoJUGLi</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45571.52083333334</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>58000</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>59</v>
+      </c>
+      <c r="I18" t="n">
+        <v>591</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>nc8W6DTp</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45571.60416666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>60449</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>59</v>
+      </c>
+      <c r="I19" t="n">
+        <v>591</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:AA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,6 +503,66 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -513,7 +573,12 @@
       <c r="B2" s="2" t="n">
         <v>45562.64583333334</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brych f 
+  ger </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">signal iduna park
@@ -564,6 +629,42 @@
         <is>
           <t>0Ija0Ej9</t>
         </is>
+      </c>
+      <c r="P2" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>78</v>
+      </c>
+      <c r="S2" t="n">
+        <v>36000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>156</v>
+      </c>
+      <c r="V2" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="W2" t="n">
+        <v>186.6666666666667</v>
+      </c>
+      <c r="X2" t="n">
+        <v>69</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>207</v>
       </c>
     </row>
     <row r="3">
@@ -575,7 +676,12 @@
       <c r="B3" s="2" t="n">
         <v>45563.4375</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schlager d 
+  ger </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">borussia park
@@ -623,6 +729,42 @@
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="R3" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="S3" t="n">
+        <v>13800</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>352</v>
+      </c>
+      <c r="V3" t="n">
+        <v>27</v>
+      </c>
+      <c r="W3" t="n">
+        <v>181</v>
+      </c>
+      <c r="X3" t="n">
+        <v>73</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>20500</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>146</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -633,7 +775,12 @@
       <c r="B4" s="2" t="n">
         <v>45563.4375</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gerach t 
+  ger </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">europa park stadion
@@ -684,6 +831,42 @@
         <is>
           <t>v9k3aY5F</t>
         </is>
+      </c>
+      <c r="P4" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>186</v>
+      </c>
+      <c r="R4" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>14500</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>282</v>
+      </c>
+      <c r="V4" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="W4" t="n">
+        <v>187.6</v>
+      </c>
+      <c r="X4" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>12200</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>337</v>
       </c>
     </row>
     <row r="5">
@@ -695,7 +878,12 @@
       <c r="B5" s="2" t="n">
         <v>45563.4375</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exner f 
+  ger </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">mewa arena
@@ -743,6 +931,42 @@
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>180</v>
+      </c>
+      <c r="R5" t="n">
+        <v>77</v>
+      </c>
+      <c r="S5" t="n">
+        <v>29000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>77</v>
+      </c>
+      <c r="V5" t="n">
+        <v>23</v>
+      </c>
+      <c r="W5" t="n">
+        <v>186</v>
+      </c>
+      <c r="X5" t="n">
+        <v>66</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>7000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -753,7 +977,12 @@
       <c r="B6" s="2" t="n">
         <v>45563.4375</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">siebert d 
+  ger </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">red bull arena
@@ -801,6 +1030,40 @@
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>181</v>
+      </c>
+      <c r="R6" t="n">
+        <v>74.66666666666667</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>224</v>
+      </c>
+      <c r="V6" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="W6" t="n">
+        <v>183</v>
+      </c>
+      <c r="X6" t="n">
+        <v>71.33333333333333</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>14333.33333333333</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>214</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -811,7 +1074,12 @@
       <c r="B7" s="2" t="n">
         <v>45563.4375</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jablonski s 
+  ger </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">volkswagen arena
@@ -862,6 +1130,42 @@
         <is>
           <t>fiEQZ7C7</t>
         </is>
+      </c>
+      <c r="P7" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="S7" t="n">
+        <v>39000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>382</v>
+      </c>
+      <c r="V7" t="n">
+        <v>21</v>
+      </c>
+      <c r="W7" t="n">
+        <v>185</v>
+      </c>
+      <c r="X7" t="n">
+        <v>71</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>12000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>142</v>
       </c>
     </row>
     <row r="8">
@@ -873,7 +1177,12 @@
       <c r="B8" s="2" t="n">
         <v>45563.5625</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">allianz arena
@@ -921,6 +1230,30 @@
           <t>WG9pOTse</t>
         </is>
       </c>
+      <c r="P8" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="S8" t="n">
+        <v>22200</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>352</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -983,6 +1316,42 @@
           <t>EuakNmc1</t>
         </is>
       </c>
+      <c r="P9" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>190.6666666666667</v>
+      </c>
+      <c r="R9" t="n">
+        <v>68</v>
+      </c>
+      <c r="S9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>204</v>
+      </c>
+      <c r="V9" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>71</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>22500</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>142</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1045,547 +1414,41 @@
           <t>v9k3aY5F</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>UajsPCkT</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45569.64583333334</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wwk arena
-  augsburg </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>30660</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>59</v>
-      </c>
-      <c r="I11" t="n">
-        <v>591</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>tbtaPLqC</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45570.4375</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bayarena
-  leverkusen </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>30210</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>63WsD2ei</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>59</v>
-      </c>
-      <c r="I12" t="n">
-        <v>591</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ENOasf5c</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45570.4375</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vonovia ruhrstadion
-  bochum </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>26000</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>59</v>
-      </c>
-      <c r="I13" t="n">
-        <v>591</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0Ija0Ej9</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>lpXDJjDj</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45570.4375</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadion an der alten forsterei
-  berlin </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>22012</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>pzHW4oaE</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>59</v>
-      </c>
-      <c r="I14" t="n">
-        <v>591</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>0Ija0Ej9</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>dnhZQYKG</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45570.4375</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">weserstadion
-  bremen </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>42100</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>59</v>
-      </c>
-      <c r="I15" t="n">
-        <v>591</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>zwD8uYZ9</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45570.5625</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">millerntor stadion
-  hamburg </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>29546</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>59</v>
-      </c>
-      <c r="I16" t="n">
-        <v>591</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>0KbQSfj4</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45571.4375</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">voith arena
-  heidenheim </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KbS1suSm</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>59</v>
-      </c>
-      <c r="I17" t="n">
-        <v>591</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>ShoJUGLi</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45571.52083333334</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">deutsche bank park
-  frankfurt </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>58000</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>nVp0wiqd</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>59</v>
-      </c>
-      <c r="I18" t="n">
-        <v>591</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>nc8W6DTp</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45571.60416666666</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mhparena
-  stuttgart </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>60449</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>hQAtP9Sl</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>59</v>
-      </c>
-      <c r="I19" t="n">
-        <v>591</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
+      <c r="P10" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>181</v>
+      </c>
+      <c r="R10" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="S10" t="n">
+        <v>28200</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>374</v>
+      </c>
+      <c r="V10" t="n">
+        <v>26</v>
+      </c>
+      <c r="W10" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>18500</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA3"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,42 +495,42 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>id_team_home_rival_team</t>
+          <t>mean_age_player_miss_home</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>id_team_away_rival_team</t>
+          <t>mean_hei_player_miss_home</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>n_player_miss_home</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>sum_rat_player_miss_home</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_miss_home</t>
+          <t>sum_wage_player_miss_home</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_miss_home</t>
+          <t>sum_value_player_miss_home</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>sum_pot_player_miss_home</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>sum_rep_player_miss_home</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
@@ -545,57 +545,67 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_miss_away</t>
+          <t>n_player_miss_away</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_miss_away</t>
+          <t>sum_rat_player_miss_away</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>sum_wage_player_miss_away</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_away</t>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pWnjRsFa</t>
+          <t>UajsPCkT</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45564.4375</v>
+        <v>45569.64583333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">badstubner f 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">holstein stadion
-  kiel </t>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>15034</v>
+        <v>30660</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -620,155 +630,1266 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
+      <c r="N2" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="O2" t="n">
+        <v>180.6</v>
       </c>
       <c r="P2" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="Q2" t="n">
-        <v>193.5</v>
+        <v>348</v>
       </c>
       <c r="R2" t="n">
-        <v>68.5</v>
+        <v>83000</v>
       </c>
       <c r="S2" t="n">
-        <v>8500</v>
+        <v>13325000</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>361</v>
       </c>
       <c r="U2" t="n">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="V2" t="n">
-        <v>19</v>
+        <v>23.5</v>
       </c>
       <c r="W2" t="n">
-        <v>172</v>
+        <v>182.8333333333333</v>
       </c>
       <c r="X2" t="n">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="Y2" t="n">
-        <v>3000</v>
+        <v>424</v>
       </c>
       <c r="Z2" t="n">
-        <v>1</v>
+        <v>96000</v>
       </c>
       <c r="AA2" t="n">
-        <v>59</v>
+        <v>39725000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>466</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bFO8E4Vg</t>
+          <t>tbtaPLqC</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45564.52083333334</v>
-      </c>
-      <c r="C3" t="inlineStr">
+        <v>45570.4375</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>59</v>
+      </c>
+      <c r="I3" t="n">
+        <v>591</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="n">
+        <v>25</v>
+      </c>
+      <c r="W3" t="n">
+        <v>193.5</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>138</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>29000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>147</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ENOasf5c</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burda m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>59</v>
+      </c>
+      <c r="I4" t="n">
+        <v>591</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>24</v>
+      </c>
+      <c r="O4" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>136</v>
+      </c>
+      <c r="R4" t="n">
+        <v>32000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5575000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>147</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>23.57142857142857</v>
+      </c>
+      <c r="W4" t="n">
+        <v>182.5714285714286</v>
+      </c>
+      <c r="X4" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>520</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>244000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>76100000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>558</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>lpXDJjDj</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t xml:space="preserve">reichel t 
   ger </t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>22012</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>59</v>
+      </c>
+      <c r="I5" t="n">
+        <v>591</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>28</v>
+      </c>
+      <c r="O5" t="n">
+        <v>181</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>146</v>
+      </c>
+      <c r="R5" t="n">
+        <v>58000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8600000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>146</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="W5" t="n">
+        <v>180.3333333333333</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>237</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>133000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>92500000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>253</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>dnhZQYKG</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">welz t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>42100</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>59</v>
+      </c>
+      <c r="I6" t="n">
+        <v>591</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>189</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>147</v>
+      </c>
+      <c r="R6" t="n">
+        <v>46000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>148</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
+      </c>
+      <c r="V6" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="W6" t="n">
+        <v>185.8333333333333</v>
+      </c>
+      <c r="X6" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>423</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>101000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>26000000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>454</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>zwD8uYZ9</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45570.5625</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>29546</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>59</v>
+      </c>
+      <c r="I7" t="n">
+        <v>591</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>187</v>
+      </c>
+      <c r="P7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>326</v>
+      </c>
+      <c r="R7" t="n">
+        <v>71000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3310000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>335</v>
+      </c>
+      <c r="U7" t="n">
+        <v>5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>27</v>
+      </c>
+      <c r="W7" t="n">
+        <v>185</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>76</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>26000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>78</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>0KbQSfj4</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45571.4375</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>59</v>
+      </c>
+      <c r="I8" t="n">
+        <v>591</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>186.8</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>349</v>
+      </c>
+      <c r="R8" t="n">
+        <v>100000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>14600000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>370</v>
+      </c>
+      <c r="U8" t="n">
+        <v>6</v>
+      </c>
+      <c r="V8" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="W8" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>308</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>184000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>70500000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>332</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ShoJUGLi</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45571.52083333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>58000</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>59</v>
+      </c>
+      <c r="I9" t="n">
+        <v>591</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>19</v>
+      </c>
+      <c r="O9" t="n">
+        <v>172</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>59</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>575000</v>
+      </c>
+      <c r="T9" t="n">
+        <v>76</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="W9" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>444</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>276000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>189150000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>498</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>nc8W6DTp</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45571.60416666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>60449</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I10" t="n">
+        <v>591</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="O10" t="n">
+        <v>186</v>
+      </c>
+      <c r="P10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>431</v>
+      </c>
+      <c r="R10" t="n">
+        <v>116000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>32600000</v>
+      </c>
+      <c r="T10" t="n">
+        <v>471</v>
+      </c>
+      <c r="U10" t="n">
+        <v>8</v>
+      </c>
+      <c r="V10" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>371</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>142000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>30200000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>386</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>z1eeWTdd</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45583.64583333334</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>81365</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>59</v>
+      </c>
+      <c r="I11" t="n">
+        <v>591</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>fHjVr7t2</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45584.4375</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>54042</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>59</v>
+      </c>
+      <c r="I12" t="n">
+        <v>591</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>r3GGwC4M</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45584.4375</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>59</v>
+      </c>
+      <c r="I13" t="n">
+        <v>591</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>M93rhBJF</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45584.4375</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>34700</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>59</v>
+      </c>
+      <c r="I14" t="n">
+        <v>591</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Eq0zfXl3</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45584.4375</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
         <is>
           <t xml:space="preserve">prezero arena
   sinsheim </t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E15" t="n">
         <v>30150</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>hQAtP9Sl</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
         <v>59</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I15" t="n">
         <v>591</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J15" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K15" t="n">
         <v>20242025</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>25.16666666666667</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>180.6666666666667</v>
-      </c>
-      <c r="R3" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="S3" t="n">
-        <v>25333.33333333333</v>
-      </c>
-      <c r="T3" t="n">
-        <v>6</v>
-      </c>
-      <c r="U3" t="n">
-        <v>447</v>
-      </c>
-      <c r="V3" t="n">
-        <v>26</v>
-      </c>
-      <c r="W3" t="n">
-        <v>185.5</v>
-      </c>
-      <c r="X3" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>18500</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>147</v>
-      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>E7rNpTBk</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45584.4375</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>59</v>
+      </c>
+      <c r="I16" t="n">
+        <v>591</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,35 +577,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>UajsPCkT</t>
+          <t>0KbQSfj4</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45569.64583333334</v>
+        <v>45571.4375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">badstubner f 
+          <t xml:space="preserve">stegemann s 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">wwk arena
-  augsburg </t>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>30660</v>
+        <v>15000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -631,81 +631,86 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>25.6</v>
+        <v>24.25</v>
       </c>
       <c r="O2" t="n">
-        <v>180.6</v>
+        <v>189.75</v>
       </c>
       <c r="P2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>348</v>
+        <v>274</v>
       </c>
       <c r="R2" t="n">
-        <v>83000</v>
+        <v>73000</v>
       </c>
       <c r="S2" t="n">
-        <v>13325000</v>
+        <v>7600000</v>
       </c>
       <c r="T2" t="n">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="U2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V2" t="n">
-        <v>23.5</v>
+        <v>25.25</v>
       </c>
       <c r="W2" t="n">
-        <v>182.8333333333333</v>
+        <v>180.75</v>
       </c>
       <c r="X2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y2" t="n">
-        <v>424</v>
+        <v>308</v>
       </c>
       <c r="Z2" t="n">
-        <v>96000</v>
+        <v>184000</v>
       </c>
       <c r="AA2" t="n">
-        <v>39725000</v>
+        <v>70500000</v>
       </c>
       <c r="AB2" t="n">
-        <v>466</v>
+        <v>332</v>
       </c>
       <c r="AC2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>tbtaPLqC</t>
+          <t>ShoJUGLi</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45570.4375</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>45571.52083333334</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brand b 
+  ger </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bayarena
-  leverkusen </t>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>30210</v>
+        <v>58000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -730,71 +735,87 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>19</v>
+      </c>
+      <c r="O3" t="n">
+        <v>172</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>59</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>575000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>76</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
       <c r="V3" t="n">
-        <v>25</v>
+        <v>21.66666666666667</v>
       </c>
       <c r="W3" t="n">
-        <v>193.5</v>
+        <v>183.5</v>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y3" t="n">
-        <v>138</v>
+        <v>444</v>
       </c>
       <c r="Z3" t="n">
-        <v>29000</v>
+        <v>276000</v>
       </c>
       <c r="AA3" t="n">
-        <v>3800000</v>
+        <v>189150000</v>
       </c>
       <c r="AB3" t="n">
-        <v>147</v>
+        <v>498</v>
       </c>
       <c r="AC3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ENOasf5c</t>
+          <t>nc8W6DTp</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45570.4375</v>
+        <v>45571.60416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
+          <t xml:space="preserve">osmers h 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">vonovia ruhrstadion
-  bochum </t>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>26000</v>
+        <v>60449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -820,86 +841,81 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>24</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="O4" t="n">
-        <v>185.5</v>
+        <v>186</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q4" t="n">
-        <v>136</v>
+        <v>431</v>
       </c>
       <c r="R4" t="n">
-        <v>32000</v>
+        <v>116000</v>
       </c>
       <c r="S4" t="n">
-        <v>5575000</v>
+        <v>32600000</v>
       </c>
       <c r="T4" t="n">
-        <v>147</v>
+        <v>471</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="V4" t="n">
-        <v>23.57142857142857</v>
+        <v>27.8</v>
       </c>
       <c r="W4" t="n">
-        <v>182.5714285714286</v>
+        <v>182.8</v>
       </c>
       <c r="X4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="n">
-        <v>520</v>
+        <v>375</v>
       </c>
       <c r="Z4" t="n">
-        <v>244000</v>
+        <v>151000</v>
       </c>
       <c r="AA4" t="n">
-        <v>76100000</v>
+        <v>31900000</v>
       </c>
       <c r="AB4" t="n">
-        <v>558</v>
+        <v>384</v>
       </c>
       <c r="AC4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lpXDJjDj</t>
+          <t>z1eeWTdd</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45570.4375</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reichel t 
-  ger </t>
-        </is>
-      </c>
+        <v>45583.64583333334</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion an der alten forsterei
-  berlin </t>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>22012</v>
+        <v>81365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -924,87 +940,50 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N5" t="n">
-        <v>28</v>
-      </c>
-      <c r="O5" t="n">
-        <v>181</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>146</v>
-      </c>
-      <c r="R5" t="n">
-        <v>58000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>8600000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>146</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" t="n">
-        <v>22.66666666666667</v>
-      </c>
-      <c r="W5" t="n">
-        <v>180.3333333333333</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>237</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>133000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>92500000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>253</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7</v>
-      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dnhZQYKG</t>
+          <t>fHjVr7t2</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45570.4375</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">welz t 
-  ger </t>
-        </is>
-      </c>
+        <v>45584.4375</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">weserstadion
-  bremen </t>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>42100</v>
+        <v>54042</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1029,87 +1008,50 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N6" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>189</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>147</v>
-      </c>
-      <c r="R6" t="n">
-        <v>46000</v>
-      </c>
-      <c r="S6" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="T6" t="n">
-        <v>148</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2</v>
-      </c>
-      <c r="V6" t="n">
-        <v>24.66666666666667</v>
-      </c>
-      <c r="W6" t="n">
-        <v>185.8333333333333</v>
-      </c>
-      <c r="X6" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>423</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>101000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>26000000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>454</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>6</v>
-      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>zwD8uYZ9</t>
+          <t>r3GGwC4M</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45570.5625</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dingert c 
-  ger </t>
-        </is>
-      </c>
+        <v>45584.4375</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">millerntor stadion
-  hamburg </t>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>29546</v>
+        <v>30210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1134,82 +1076,50 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N7" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="O7" t="n">
-        <v>187</v>
-      </c>
-      <c r="P7" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>326</v>
-      </c>
-      <c r="R7" t="n">
-        <v>71000</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3310000</v>
-      </c>
-      <c r="T7" t="n">
-        <v>335</v>
-      </c>
-      <c r="U7" t="n">
-        <v>5</v>
-      </c>
-      <c r="V7" t="n">
-        <v>27</v>
-      </c>
-      <c r="W7" t="n">
-        <v>185</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>76</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>26000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>78</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1</v>
-      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>0KbQSfj4</t>
+          <t>M93rhBJF</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45571.4375</v>
+        <v>45584.4375</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">voith arena
-  heidenheim </t>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15000</v>
+        <v>34700</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1234,82 +1144,50 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N8" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="O8" t="n">
-        <v>186.8</v>
-      </c>
-      <c r="P8" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>349</v>
-      </c>
-      <c r="R8" t="n">
-        <v>100000</v>
-      </c>
-      <c r="S8" t="n">
-        <v>14600000</v>
-      </c>
-      <c r="T8" t="n">
-        <v>370</v>
-      </c>
-      <c r="U8" t="n">
-        <v>6</v>
-      </c>
-      <c r="V8" t="n">
-        <v>25.25</v>
-      </c>
-      <c r="W8" t="n">
-        <v>180.75</v>
-      </c>
-      <c r="X8" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>308</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>184000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>70500000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>332</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>9</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ShoJUGLi</t>
+          <t>Eq0zfXl3</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45571.52083333334</v>
+        <v>45584.4375</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">deutsche bank park
-  frankfurt </t>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>58000</v>
+        <v>30150</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1334,82 +1212,50 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N9" t="n">
-        <v>19</v>
-      </c>
-      <c r="O9" t="n">
-        <v>172</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>59</v>
-      </c>
-      <c r="R9" t="n">
-        <v>3000</v>
-      </c>
-      <c r="S9" t="n">
-        <v>575000</v>
-      </c>
-      <c r="T9" t="n">
-        <v>76</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" t="n">
-        <v>21.66666666666667</v>
-      </c>
-      <c r="W9" t="n">
-        <v>183.5</v>
-      </c>
-      <c r="X9" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>444</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>276000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>189150000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>498</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>10</v>
-      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nc8W6DTp</t>
+          <t>E7rNpTBk</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45571.60416666666</v>
+        <v>45584.4375</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">mhparena
-  stuttgart </t>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>60449</v>
+        <v>34000</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1434,82 +1280,50 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N10" t="n">
-        <v>23.33333333333333</v>
-      </c>
-      <c r="O10" t="n">
-        <v>186</v>
-      </c>
-      <c r="P10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>431</v>
-      </c>
-      <c r="R10" t="n">
-        <v>116000</v>
-      </c>
-      <c r="S10" t="n">
-        <v>32600000</v>
-      </c>
-      <c r="T10" t="n">
-        <v>471</v>
-      </c>
-      <c r="U10" t="n">
-        <v>8</v>
-      </c>
-      <c r="V10" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="W10" t="n">
-        <v>183.2</v>
-      </c>
-      <c r="X10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>371</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>142000</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>30200000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>386</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8</v>
-      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>z1eeWTdd</t>
+          <t>2mcmYkSq</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45583.64583333334</v>
+        <v>45584.5625</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">signal iduna park
-  dortmund </t>
+          <t xml:space="preserve">allianz arena
+  munich </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>81365</v>
+        <v>75024</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1554,30 +1368,30 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>fHjVr7t2</t>
+          <t>nBwH6AY8</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45584.4375</v>
+        <v>45585.4375</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">borussia park
-  monchengladbach </t>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>54042</v>
+        <v>15034</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1622,30 +1436,30 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>r3GGwC4M</t>
+          <t>rPiijklS</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45584.4375</v>
+        <v>45585.52083333334</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">bayarena
-  leverkusen </t>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>30210</v>
+        <v>28917</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1687,210 +1501,6 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>M93rhBJF</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45584.4375</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">europa park stadion
-  freiburg </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>34700</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>59</v>
-      </c>
-      <c r="I14" t="n">
-        <v>591</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Eq0zfXl3</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45584.4375</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prezero arena
-  sinsheim </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>30150</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>hQAtP9Sl</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>59</v>
-      </c>
-      <c r="I15" t="n">
-        <v>591</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>E7rNpTBk</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45584.4375</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mewa arena
-  mainz </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>34000</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KbS1suSm</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>59</v>
-      </c>
-      <c r="I16" t="n">
-        <v>591</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,86 @@
           <t>competition</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -545,6 +625,54 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N2" t="n">
+        <v>20.33333333333333</v>
+      </c>
+      <c r="O2" t="n">
+        <v>178.3333333333333</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>220</v>
+      </c>
+      <c r="R2" t="n">
+        <v>86000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>49700000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>255</v>
+      </c>
+      <c r="U2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V2" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="W2" t="n">
+        <v>187.1666666666667</v>
+      </c>
+      <c r="X2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>401</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>80000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>7210000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>420</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -597,6 +725,54 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>182.8333333333333</v>
+      </c>
+      <c r="P3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>424</v>
+      </c>
+      <c r="R3" t="n">
+        <v>96000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>39725000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>466</v>
+      </c>
+      <c r="U3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V3" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="W3" t="n">
+        <v>189.6666666666667</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>204</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>53000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>215</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -649,6 +825,54 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N4" t="n">
+        <v>21</v>
+      </c>
+      <c r="O4" t="n">
+        <v>177</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>88</v>
+      </c>
+      <c r="R4" t="n">
+        <v>115000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>133500000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>92</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4</v>
+      </c>
+      <c r="V4" t="n">
+        <v>19</v>
+      </c>
+      <c r="W4" t="n">
+        <v>172</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>575000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>76</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -701,6 +925,54 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N5" t="n">
+        <v>26</v>
+      </c>
+      <c r="O5" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>283</v>
+      </c>
+      <c r="R5" t="n">
+        <v>68000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>17900000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>298</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V5" t="n">
+        <v>25.83333333333333</v>
+      </c>
+      <c r="W5" t="n">
+        <v>182</v>
+      </c>
+      <c r="X5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>423</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>107000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>19825000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>439</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -753,6 +1025,54 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N6" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="O6" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>375</v>
+      </c>
+      <c r="R6" t="n">
+        <v>151000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>31900000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>384</v>
+      </c>
+      <c r="U6" t="n">
+        <v>9</v>
+      </c>
+      <c r="V6" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>183</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>133</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>29000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2975000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>144</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -805,6 +1125,54 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N7" t="n">
+        <v>30</v>
+      </c>
+      <c r="O7" t="n">
+        <v>183</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>75</v>
+      </c>
+      <c r="R7" t="n">
+        <v>26000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>75</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="W7" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="X7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>309</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>192000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>71500000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>332</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -857,6 +1225,54 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N8" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>185</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>382</v>
+      </c>
+      <c r="R8" t="n">
+        <v>255000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>188150000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>420</v>
+      </c>
+      <c r="U8" t="n">
+        <v>9</v>
+      </c>
+      <c r="V8" t="n">
+        <v>22.57142857142857</v>
+      </c>
+      <c r="W8" t="n">
+        <v>184.8571428571429</v>
+      </c>
+      <c r="X8" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>497</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>138000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>48550000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>552</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -909,6 +1325,22 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -961,6 +1393,22 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1013,6 +1461,22 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1065,6 +1529,22 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1117,6 +1597,22 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1169,6 +1665,22 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1221,6 +1733,22 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1273,6 +1801,22 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1325,6 +1869,22 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1377,6 +1937,22 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1429,6 +2005,22 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
@@ -583,7 +583,12 @@
       <c r="B2" s="2" t="n">
         <v>45583.64583333334</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jollenbeck m 
+  ger </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">signal iduna park
@@ -650,28 +655,28 @@
         <v>5</v>
       </c>
       <c r="V2" t="n">
-        <v>27.33333333333333</v>
+        <v>27</v>
       </c>
       <c r="W2" t="n">
-        <v>187.1666666666667</v>
+        <v>186.75</v>
       </c>
       <c r="X2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y2" t="n">
-        <v>401</v>
+        <v>535</v>
       </c>
       <c r="Z2" t="n">
-        <v>80000</v>
+        <v>111000</v>
       </c>
       <c r="AA2" t="n">
-        <v>7210000</v>
+        <v>9810000</v>
       </c>
       <c r="AB2" t="n">
-        <v>420</v>
+        <v>559</v>
       </c>
       <c r="AC2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -726,52 +731,52 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>23.5</v>
+        <v>22.8</v>
       </c>
       <c r="O3" t="n">
-        <v>182.8333333333333</v>
+        <v>183.4</v>
       </c>
       <c r="P3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>345</v>
+      </c>
+      <c r="R3" t="n">
+        <v>62000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>21225000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>387</v>
+      </c>
+      <c r="U3" t="n">
         <v>6</v>
       </c>
-      <c r="Q3" t="n">
-        <v>424</v>
-      </c>
-      <c r="R3" t="n">
-        <v>96000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>39725000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>466</v>
-      </c>
-      <c r="U3" t="n">
-        <v>8</v>
-      </c>
       <c r="V3" t="n">
-        <v>24.66666666666667</v>
+        <v>25</v>
       </c>
       <c r="W3" t="n">
-        <v>189.6666666666667</v>
+        <v>186</v>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y3" t="n">
-        <v>204</v>
+        <v>279</v>
       </c>
       <c r="Z3" t="n">
-        <v>53000</v>
+        <v>80000</v>
       </c>
       <c r="AA3" t="n">
-        <v>5100000</v>
+        <v>12100000</v>
       </c>
       <c r="AB3" t="n">
-        <v>215</v>
+        <v>294</v>
       </c>
       <c r="AC3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -926,28 +931,28 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>26</v>
+        <v>23.66666666666667</v>
       </c>
       <c r="O5" t="n">
-        <v>185.5</v>
+        <v>186</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>283</v>
+        <v>210</v>
       </c>
       <c r="R5" t="n">
-        <v>68000</v>
+        <v>46000</v>
       </c>
       <c r="S5" t="n">
-        <v>17900000</v>
+        <v>16400000</v>
       </c>
       <c r="T5" t="n">
-        <v>298</v>
+        <v>225</v>
       </c>
       <c r="U5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
         <v>25.83333333333333</v>
@@ -1026,52 +1031,52 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>27.8</v>
+        <v>27.33333333333333</v>
       </c>
       <c r="O6" t="n">
-        <v>182.8</v>
+        <v>183</v>
       </c>
       <c r="P6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q6" t="n">
-        <v>375</v>
+        <v>447</v>
       </c>
       <c r="R6" t="n">
-        <v>151000</v>
+        <v>174000</v>
       </c>
       <c r="S6" t="n">
-        <v>31900000</v>
+        <v>35200000</v>
       </c>
       <c r="T6" t="n">
-        <v>384</v>
+        <v>462</v>
       </c>
       <c r="U6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V6" t="n">
-        <v>23.5</v>
+        <v>25.33333333333333</v>
       </c>
       <c r="W6" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="n">
-        <v>133</v>
+        <v>208</v>
       </c>
       <c r="Z6" t="n">
-        <v>29000</v>
+        <v>52000</v>
       </c>
       <c r="AA6" t="n">
-        <v>2975000</v>
+        <v>7875000</v>
       </c>
       <c r="AB6" t="n">
-        <v>144</v>
+        <v>219</v>
       </c>
       <c r="AC6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -1126,52 +1131,52 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O7" t="n">
-        <v>183</v>
+        <v>185.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>75</v>
+        <v>148</v>
       </c>
       <c r="R7" t="n">
-        <v>26000</v>
+        <v>51000</v>
       </c>
       <c r="S7" t="n">
-        <v>4600000</v>
+        <v>7100000</v>
       </c>
       <c r="T7" t="n">
-        <v>75</v>
+        <v>148</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V7" t="n">
-        <v>25.75</v>
+        <v>24.25</v>
       </c>
       <c r="W7" t="n">
-        <v>180.75</v>
+        <v>182</v>
       </c>
       <c r="X7" t="n">
         <v>4</v>
       </c>
       <c r="Y7" t="n">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Z7" t="n">
-        <v>192000</v>
+        <v>200000</v>
       </c>
       <c r="AA7" t="n">
-        <v>71500000</v>
+        <v>90000000</v>
       </c>
       <c r="AB7" t="n">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="AC7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -1226,52 +1231,52 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>22.4</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="O8" t="n">
-        <v>185</v>
+        <v>185.1666666666667</v>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="n">
-        <v>382</v>
+        <v>464</v>
       </c>
       <c r="R8" t="n">
-        <v>255000</v>
+        <v>324000</v>
       </c>
       <c r="S8" t="n">
-        <v>188150000</v>
+        <v>224150000</v>
       </c>
       <c r="T8" t="n">
-        <v>420</v>
+        <v>505</v>
       </c>
       <c r="U8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="V8" t="n">
-        <v>22.57142857142857</v>
+        <v>22.5</v>
       </c>
       <c r="W8" t="n">
-        <v>184.8571428571429</v>
+        <v>184</v>
       </c>
       <c r="X8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y8" t="n">
-        <v>497</v>
+        <v>422</v>
       </c>
       <c r="Z8" t="n">
-        <v>138000</v>
+        <v>117000</v>
       </c>
       <c r="AA8" t="n">
-        <v>48550000</v>
+        <v>41050000</v>
       </c>
       <c r="AB8" t="n">
-        <v>552</v>
+        <v>473</v>
       </c>
       <c r="AC8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -1325,22 +1330,54 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>190</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>136</v>
+      </c>
+      <c r="R9" t="n">
+        <v>27000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="T9" t="n">
+        <v>145</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" t="n">
+        <v>29</v>
+      </c>
+      <c r="W9" t="n">
+        <v>180.3333333333333</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>222</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>94000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>15100000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>222</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">

--- a/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,285 +493,941 @@
           <t>competition</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_home</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_home</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_home</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_home</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>sum_wage_player_miss_home</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>sum_value_player_miss_home</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_home</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rep_player_miss_home</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_away</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_away</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>sum_wage_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>sum_value_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rep_player_miss_away</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nBwH6AY8</t>
+          <t>4E8uaJWa</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45585.4375</v>
+        <v>45590.64583333334</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>59</v>
+      </c>
+      <c r="I2" t="n">
+        <v>591</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>x0haJmIE</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45591.4375</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>30660</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>59</v>
+      </c>
+      <c r="I3" t="n">
+        <v>591</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ELNeaSQr</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45591.4375</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>47069</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>59</v>
+      </c>
+      <c r="I4" t="n">
+        <v>591</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Mku6FvHt</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45591.4375</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>29546</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>59</v>
+      </c>
+      <c r="I5" t="n">
+        <v>591</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>rwXP4l3L</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45591.4375</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>60449</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>59</v>
+      </c>
+      <c r="I6" t="n">
+        <v>591</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>MiACepQ7</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45591.5625</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>42100</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>59</v>
+      </c>
+      <c r="I7" t="n">
+        <v>591</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WQadeyWO</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45592.47916666666</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>59</v>
+      </c>
+      <c r="I8" t="n">
+        <v>591</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ABBmcc1C</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45592.5625</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>22012</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>59</v>
+      </c>
+      <c r="I9" t="n">
+        <v>591</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>zyC4c6ee</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45592.64583333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I10" t="n">
+        <v>591</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>IHYEDIog</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45597.6875</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>59</v>
+      </c>
+      <c r="I11" t="n">
+        <v>591</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>jVWMBdG5</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz arena
+  munich </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>75024</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>59</v>
+      </c>
+      <c r="I12" t="n">
+        <v>591</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>485V7EFU</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>58000</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>59</v>
+      </c>
+      <c r="I13" t="n">
+        <v>591</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8MVuSH0n</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>30150</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>59</v>
+      </c>
+      <c r="I14" t="n">
+        <v>591</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>2q7yHiho</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
           <t xml:space="preserve">holstein stadion
   kiel </t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E15" t="n">
         <v>15034</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>63WsD2ei</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>pzHW4oaE</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>59</v>
-      </c>
-      <c r="I2" t="n">
-        <v>591</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>190</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>136</v>
-      </c>
-      <c r="R2" t="n">
-        <v>27000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>145</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V2" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="W2" t="n">
-        <v>181.5</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>298</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>125000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>23600000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>301</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>rPiijklS</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45585.52083333334</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>59</v>
+      </c>
+      <c r="I15" t="n">
+        <v>591</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AoSdOZaB</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t xml:space="preserve">volkswagen arena
   wolfsburg </t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E16" t="n">
         <v>28917</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>nwkTahLL</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>59</v>
+      </c>
+      <c r="I16" t="n">
+        <v>591</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>dr2N9zoI</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45598.60416666666</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>81365</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>59</v>
+      </c>
+      <c r="I17" t="n">
+        <v>591</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>GnZmQeVb</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45599.47916666666</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>34700</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>59</v>
+      </c>
+      <c r="I18" t="n">
+        <v>591</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>raQ4MDUN</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45599.5625</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>54042</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>Ig1f1fy3</t>
         </is>
       </c>
-      <c r="H3" t="n">
-        <v>59</v>
-      </c>
-      <c r="I3" t="n">
-        <v>591</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="O3" t="n">
-        <v>182.8</v>
-      </c>
-      <c r="P3" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>371</v>
-      </c>
-      <c r="R3" t="n">
-        <v>181000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>56300000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>398</v>
-      </c>
-      <c r="U3" t="n">
-        <v>8</v>
-      </c>
-      <c r="V3" t="n">
-        <v>26.66666666666667</v>
-      </c>
-      <c r="W3" t="n">
-        <v>187</v>
-      </c>
-      <c r="X3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>440</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>135000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>26600000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>455</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>6</v>
+      <c r="H19" t="n">
+        <v>59</v>
+      </c>
+      <c r="I19" t="n">
+        <v>591</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,86 @@
           <t>competition</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -503,7 +583,12 @@
       <c r="B2" s="2" t="n">
         <v>45590.64583333334</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">petersen m 
+  ger </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">mewa arena
@@ -544,6 +629,54 @@
         <is>
           <t>bundesliga</t>
         </is>
+      </c>
+      <c r="N2" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="O2" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>149</v>
+      </c>
+      <c r="R2" t="n">
+        <v>51000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>151</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V2" t="n">
+        <v>23.14285714285714</v>
+      </c>
+      <c r="W2" t="n">
+        <v>184.2857142857143</v>
+      </c>
+      <c r="X2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>495</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>105000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>34225000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>542</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +688,12 @@
       <c r="B3" s="2" t="n">
         <v>45591.4375</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">welz t 
+  ger </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">wwk arena
@@ -596,6 +734,54 @@
         <is>
           <t>bundesliga</t>
         </is>
+      </c>
+      <c r="N3" t="n">
+        <v>26</v>
+      </c>
+      <c r="O3" t="n">
+        <v>184</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>362</v>
+      </c>
+      <c r="R3" t="n">
+        <v>98000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>371</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V3" t="n">
+        <v>23</v>
+      </c>
+      <c r="W3" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="X3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>381</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>193000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>97700000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>418</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -607,7 +793,12 @@
       <c r="B4" s="2" t="n">
         <v>45591.4375</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jablonski s 
+  ger </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">red bull arena
@@ -648,6 +839,54 @@
         <is>
           <t>bundesliga</t>
         </is>
+      </c>
+      <c r="N4" t="n">
+        <v>23.66666666666667</v>
+      </c>
+      <c r="O4" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="P4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>470</v>
+      </c>
+      <c r="R4" t="n">
+        <v>313000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>158000000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>507</v>
+      </c>
+      <c r="U4" t="n">
+        <v>12</v>
+      </c>
+      <c r="V4" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="W4" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="X4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>350</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>83000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>374</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -659,7 +898,12 @@
       <c r="B5" s="2" t="n">
         <v>45591.4375</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reichel t 
+  ger </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">millerntor stadion
@@ -700,6 +944,54 @@
         <is>
           <t>bundesliga</t>
         </is>
+      </c>
+      <c r="N5" t="n">
+        <v>24.57142857142857</v>
+      </c>
+      <c r="O5" t="n">
+        <v>186.7142857142857</v>
+      </c>
+      <c r="P5" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>473</v>
+      </c>
+      <c r="R5" t="n">
+        <v>98000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>13640000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>507</v>
+      </c>
+      <c r="U5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V5" t="n">
+        <v>24.57142857142857</v>
+      </c>
+      <c r="W5" t="n">
+        <v>182.8571428571429</v>
+      </c>
+      <c r="X5" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>528</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>271000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>90300000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>561</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -711,7 +1003,12 @@
       <c r="B6" s="2" t="n">
         <v>45591.4375</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">mhparena
@@ -752,6 +1049,54 @@
         <is>
           <t>bundesliga</t>
         </is>
+      </c>
+      <c r="N6" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>184</v>
+      </c>
+      <c r="P6" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>422</v>
+      </c>
+      <c r="R6" t="n">
+        <v>117000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>41050000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>473</v>
+      </c>
+      <c r="U6" t="n">
+        <v>8</v>
+      </c>
+      <c r="V6" t="n">
+        <v>28</v>
+      </c>
+      <c r="W6" t="n">
+        <v>185.3333333333333</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>210</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>49000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>6100000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>219</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -763,7 +1108,12 @@
       <c r="B7" s="2" t="n">
         <v>45591.5625</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badstubner f 
+  ger </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">weserstadion
@@ -804,6 +1154,54 @@
         <is>
           <t>bundesliga</t>
         </is>
+      </c>
+      <c r="N7" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>186.8</v>
+      </c>
+      <c r="P7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>367</v>
+      </c>
+      <c r="R7" t="n">
+        <v>113000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>382</v>
+      </c>
+      <c r="U7" t="n">
+        <v>5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>182</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>160</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>150000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>77000000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>173</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -857,6 +1255,54 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N8" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>277</v>
+      </c>
+      <c r="R8" t="n">
+        <v>70000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>9375000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>288</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
+      </c>
+      <c r="V8" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W8" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="X8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>368</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>195000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>67150000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>412</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -909,6 +1355,54 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N9" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>298</v>
+      </c>
+      <c r="R9" t="n">
+        <v>125000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>23600000</v>
+      </c>
+      <c r="T9" t="n">
+        <v>301</v>
+      </c>
+      <c r="U9" t="n">
+        <v>6</v>
+      </c>
+      <c r="V9" t="n">
+        <v>20</v>
+      </c>
+      <c r="W9" t="n">
+        <v>180</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>197</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>37000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>13075000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>238</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -961,473 +1455,53 @@
           <t>bundesliga</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>IHYEDIog</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45597.6875</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bayarena
-  leverkusen </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>30210</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>59</v>
-      </c>
-      <c r="I11" t="n">
-        <v>591</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>jVWMBdG5</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45598.47916666666</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allianz arena
-  munich </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>75024</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>nVp0wiqd</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>pzHW4oaE</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>59</v>
-      </c>
-      <c r="I12" t="n">
-        <v>591</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>485V7EFU</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45598.47916666666</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">deutsche bank park
-  frankfurt </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>58000</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>59</v>
-      </c>
-      <c r="I13" t="n">
-        <v>591</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8MVuSH0n</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45598.47916666666</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prezero arena
-  sinsheim </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>30150</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>hQAtP9Sl</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>59</v>
-      </c>
-      <c r="I14" t="n">
-        <v>591</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>2q7yHiho</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45598.47916666666</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">holstein stadion
-  kiel </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>15034</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>63WsD2ei</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>59</v>
-      </c>
-      <c r="I15" t="n">
-        <v>591</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>AoSdOZaB</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45598.47916666666</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">volkswagen arena
-  wolfsburg </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>28917</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>59</v>
-      </c>
-      <c r="I16" t="n">
-        <v>591</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>dr2N9zoI</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45598.60416666666</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">signal iduna park
-  dortmund </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>81365</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KbS1suSm</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>59</v>
-      </c>
-      <c r="I17" t="n">
-        <v>591</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>GnZmQeVb</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45599.47916666666</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">europa park stadion
-  freiburg </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>34700</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>59</v>
-      </c>
-      <c r="I18" t="n">
-        <v>591</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>raQ4MDUN</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45599.5625</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">borussia park
-  monchengladbach </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>54042</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>59</v>
-      </c>
-      <c r="I19" t="n">
-        <v>591</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
+      <c r="N10" t="n">
+        <v>24</v>
+      </c>
+      <c r="O10" t="n">
+        <v>186</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>66</v>
+      </c>
+      <c r="R10" t="n">
+        <v>16000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="T10" t="n">
+        <v>70</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>27</v>
+      </c>
+      <c r="W10" t="n">
+        <v>184</v>
+      </c>
+      <c r="X10" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>600</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>228000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>58900000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>619</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,86 @@
           <t>competition</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -545,6 +625,54 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N2" t="n">
+        <v>24</v>
+      </c>
+      <c r="O2" t="n">
+        <v>174</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>78</v>
+      </c>
+      <c r="R2" t="n">
+        <v>64000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>28500000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>85</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>186.3333333333333</v>
+      </c>
+      <c r="X2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>420</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>110000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>33550000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>474</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -597,6 +725,54 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N3" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="O3" t="n">
+        <v>185.8333333333333</v>
+      </c>
+      <c r="P3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>450</v>
+      </c>
+      <c r="R3" t="n">
+        <v>264000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>103150000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>497</v>
+      </c>
+      <c r="U3" t="n">
+        <v>9</v>
+      </c>
+      <c r="V3" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="W3" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>222</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>89000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>17100000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>225</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -649,6 +825,54 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N4" t="n">
+        <v>19</v>
+      </c>
+      <c r="O4" t="n">
+        <v>180</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>121</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>157</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="W4" t="n">
+        <v>184</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>208</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>52000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>7875000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>219</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -701,6 +925,54 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N5" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="O5" t="n">
+        <v>183</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>299</v>
+      </c>
+      <c r="R5" t="n">
+        <v>119000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>26900000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>308</v>
+      </c>
+      <c r="U5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V5" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="W5" t="n">
+        <v>189.25</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>265</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>6140000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>284</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -753,6 +1025,54 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N6" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="O6" t="n">
+        <v>185.4</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>346</v>
+      </c>
+      <c r="R6" t="n">
+        <v>81000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>9900000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>363</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>22</v>
+      </c>
+      <c r="W6" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>125</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>28000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>140</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -805,6 +1125,54 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N7" t="n">
+        <v>23.14285714285714</v>
+      </c>
+      <c r="O7" t="n">
+        <v>184.5714285714286</v>
+      </c>
+      <c r="P7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>519</v>
+      </c>
+      <c r="R7" t="n">
+        <v>232000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>69300000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>559</v>
+      </c>
+      <c r="U7" t="n">
+        <v>10</v>
+      </c>
+      <c r="V7" t="n">
+        <v>26</v>
+      </c>
+      <c r="W7" t="n">
+        <v>181.3333333333333</v>
+      </c>
+      <c r="X7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>434</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>119000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>21300000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>441</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -857,6 +1225,54 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N8" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="O8" t="n">
+        <v>185.125</v>
+      </c>
+      <c r="P8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>615</v>
+      </c>
+      <c r="R8" t="n">
+        <v>324000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>211500000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>673</v>
+      </c>
+      <c r="U8" t="n">
+        <v>17</v>
+      </c>
+      <c r="V8" t="n">
+        <v>23</v>
+      </c>
+      <c r="W8" t="n">
+        <v>180</v>
+      </c>
+      <c r="X8" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>476</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>342000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>212500000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>514</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -909,6 +1325,54 @@
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="N9" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="P9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>350</v>
+      </c>
+      <c r="R9" t="n">
+        <v>83000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="T9" t="n">
+        <v>374</v>
+      </c>
+      <c r="U9" t="n">
+        <v>5</v>
+      </c>
+      <c r="V9" t="n">
+        <v>25</v>
+      </c>
+      <c r="W9" t="n">
+        <v>185.3333333333333</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>226</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>84000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>25500000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>238</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -961,473 +1425,53 @@
           <t>bundesliga</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>v3DAZKP9</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45604.6875</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadion an der alten forsterei
-  berlin </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>22012</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>pzHW4oaE</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>59</v>
-      </c>
-      <c r="I11" t="n">
-        <v>591</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>biQrHC9r</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45605.47916666666</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vonovia ruhrstadion
-  bochum </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>26000</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>59</v>
-      </c>
-      <c r="I12" t="n">
-        <v>591</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>nee3ysec</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45605.47916666666</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mewa arena
-  mainz </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>34000</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>59</v>
-      </c>
-      <c r="I13" t="n">
-        <v>591</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>6HTjFjve</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45605.47916666666</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">millerntor stadion
-  hamburg </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>29546</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>nVp0wiqd</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>59</v>
-      </c>
-      <c r="I14" t="n">
-        <v>591</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>YmumZjET</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45605.47916666666</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">weserstadion
-  bremen </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>42100</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>63WsD2ei</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>59</v>
-      </c>
-      <c r="I15" t="n">
-        <v>591</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>j5mWxZE4</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45605.60416666666</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">red bull arena
-  leipzig </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>47069</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>KbS1suSm</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>59</v>
-      </c>
-      <c r="I16" t="n">
-        <v>591</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>UJQITUyi</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45606.47916666666</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wwk arena
-  augsburg </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>30660</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>hQAtP9Sl</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>59</v>
-      </c>
-      <c r="I17" t="n">
-        <v>591</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>UkaNveph</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45606.5625</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mhparena
-  stuttgart </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>60449</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>59</v>
-      </c>
-      <c r="I18" t="n">
-        <v>591</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>xMovyDqH</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45606.64583333334</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">voith arena
-  heidenheim </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>59</v>
-      </c>
-      <c r="I19" t="n">
-        <v>591</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
+      <c r="N10" t="n">
+        <v>23.14285714285714</v>
+      </c>
+      <c r="O10" t="n">
+        <v>184.2857142857143</v>
+      </c>
+      <c r="P10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>495</v>
+      </c>
+      <c r="R10" t="n">
+        <v>105000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>34225000</v>
+      </c>
+      <c r="T10" t="n">
+        <v>542</v>
+      </c>
+      <c r="U10" t="n">
+        <v>9</v>
+      </c>
+      <c r="V10" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="W10" t="n">
+        <v>187.25</v>
+      </c>
+      <c r="X10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>292</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>90000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>17500000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>304</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,114 +493,34 @@
           <t>competition</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_home</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_home</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_home</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_home</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>sum_wage_player_miss_home</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>sum_value_player_miss_home</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_home</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rep_player_miss_home</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_away</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_away</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>sum_wage_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>sum_value_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rep_player_miss_away</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IHYEDIog</t>
+          <t>v3DAZKP9</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45597.6875</v>
+        <v>45604.6875</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bayarena
-  leverkusen </t>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>30210</v>
+        <v>22012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -624,83 +544,35 @@
         <is>
           <t>bundesliga</t>
         </is>
-      </c>
-      <c r="N2" t="n">
-        <v>24</v>
-      </c>
-      <c r="O2" t="n">
-        <v>174</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>78</v>
-      </c>
-      <c r="R2" t="n">
-        <v>64000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>28500000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>85</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="W2" t="n">
-        <v>186.3333333333333</v>
-      </c>
-      <c r="X2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>420</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>110000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>33550000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>474</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jVWMBdG5</t>
+          <t>biQrHC9r</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45598.47916666666</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz arena
-  munich </t>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>75024</v>
+        <v>26000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -724,83 +596,35 @@
         <is>
           <t>bundesliga</t>
         </is>
-      </c>
-      <c r="N3" t="n">
-        <v>22.66666666666667</v>
-      </c>
-      <c r="O3" t="n">
-        <v>185.8333333333333</v>
-      </c>
-      <c r="P3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>450</v>
-      </c>
-      <c r="R3" t="n">
-        <v>264000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>103150000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>497</v>
-      </c>
-      <c r="U3" t="n">
-        <v>9</v>
-      </c>
-      <c r="V3" t="n">
-        <v>27.66666666666667</v>
-      </c>
-      <c r="W3" t="n">
-        <v>182.3333333333333</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>222</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>89000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>17100000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>225</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>485V7EFU</t>
+          <t>nee3ysec</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45598.47916666666</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">deutsche bank park
-  frankfurt </t>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>58000</v>
+        <v>34000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -824,83 +648,35 @@
         <is>
           <t>bundesliga</t>
         </is>
-      </c>
-      <c r="N4" t="n">
-        <v>19</v>
-      </c>
-      <c r="O4" t="n">
-        <v>180</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>121</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1575000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>157</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2</v>
-      </c>
-      <c r="V4" t="n">
-        <v>25.33333333333333</v>
-      </c>
-      <c r="W4" t="n">
-        <v>184</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>208</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>52000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>7875000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>219</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8MVuSH0n</t>
+          <t>6HTjFjve</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45598.47916666666</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">prezero arena
-  sinsheim </t>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>30150</v>
+        <v>29546</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -924,83 +700,35 @@
         <is>
           <t>bundesliga</t>
         </is>
-      </c>
-      <c r="N5" t="n">
-        <v>26.75</v>
-      </c>
-      <c r="O5" t="n">
-        <v>183</v>
-      </c>
-      <c r="P5" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>299</v>
-      </c>
-      <c r="R5" t="n">
-        <v>119000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>26900000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>308</v>
-      </c>
-      <c r="U5" t="n">
-        <v>7</v>
-      </c>
-      <c r="V5" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="W5" t="n">
-        <v>189.25</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>265</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>50000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>6140000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>284</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2q7yHiho</t>
+          <t>YmumZjET</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45598.47916666666</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">holstein stadion
-  kiel </t>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>15034</v>
+        <v>42100</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>63WsD2ei</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1024,83 +752,35 @@
         <is>
           <t>bundesliga</t>
         </is>
-      </c>
-      <c r="N6" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="O6" t="n">
-        <v>185.4</v>
-      </c>
-      <c r="P6" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>346</v>
-      </c>
-      <c r="R6" t="n">
-        <v>81000</v>
-      </c>
-      <c r="S6" t="n">
-        <v>9900000</v>
-      </c>
-      <c r="T6" t="n">
-        <v>363</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" t="n">
-        <v>22</v>
-      </c>
-      <c r="W6" t="n">
-        <v>184.5</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>125</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>28000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1575000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>140</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>AoSdOZaB</t>
+          <t>j5mWxZE4</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45598.47916666666</v>
+        <v>45605.60416666666</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">volkswagen arena
-  wolfsburg </t>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>28917</v>
+        <v>47069</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1124,83 +804,35 @@
         <is>
           <t>bundesliga</t>
         </is>
-      </c>
-      <c r="N7" t="n">
-        <v>23.14285714285714</v>
-      </c>
-      <c r="O7" t="n">
-        <v>184.5714285714286</v>
-      </c>
-      <c r="P7" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>519</v>
-      </c>
-      <c r="R7" t="n">
-        <v>232000</v>
-      </c>
-      <c r="S7" t="n">
-        <v>69300000</v>
-      </c>
-      <c r="T7" t="n">
-        <v>559</v>
-      </c>
-      <c r="U7" t="n">
-        <v>10</v>
-      </c>
-      <c r="V7" t="n">
-        <v>26</v>
-      </c>
-      <c r="W7" t="n">
-        <v>181.3333333333333</v>
-      </c>
-      <c r="X7" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>434</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>119000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>21300000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>441</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dr2N9zoI</t>
+          <t>UJQITUyi</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45598.60416666666</v>
+        <v>45606.47916666666</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">signal iduna park
-  dortmund </t>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>81365</v>
+        <v>30660</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1224,83 +856,35 @@
         <is>
           <t>bundesliga</t>
         </is>
-      </c>
-      <c r="N8" t="n">
-        <v>23.25</v>
-      </c>
-      <c r="O8" t="n">
-        <v>185.125</v>
-      </c>
-      <c r="P8" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>615</v>
-      </c>
-      <c r="R8" t="n">
-        <v>324000</v>
-      </c>
-      <c r="S8" t="n">
-        <v>211500000</v>
-      </c>
-      <c r="T8" t="n">
-        <v>673</v>
-      </c>
-      <c r="U8" t="n">
-        <v>17</v>
-      </c>
-      <c r="V8" t="n">
-        <v>23</v>
-      </c>
-      <c r="W8" t="n">
-        <v>180</v>
-      </c>
-      <c r="X8" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>476</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>342000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>212500000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>514</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>GnZmQeVb</t>
+          <t>UkaNveph</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45599.47916666666</v>
+        <v>45606.5625</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">europa park stadion
-  freiburg </t>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>34700</v>
+        <v>60449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1324,83 +908,35 @@
         <is>
           <t>bundesliga</t>
         </is>
-      </c>
-      <c r="N9" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>185.8</v>
-      </c>
-      <c r="P9" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>350</v>
-      </c>
-      <c r="R9" t="n">
-        <v>83000</v>
-      </c>
-      <c r="S9" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="T9" t="n">
-        <v>374</v>
-      </c>
-      <c r="U9" t="n">
-        <v>5</v>
-      </c>
-      <c r="V9" t="n">
-        <v>25</v>
-      </c>
-      <c r="W9" t="n">
-        <v>185.3333333333333</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>226</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>84000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>25500000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>238</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>raQ4MDUN</t>
+          <t>xMovyDqH</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45599.5625</v>
+        <v>45606.64583333334</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">borussia park
-  monchengladbach </t>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>54042</v>
+        <v>15000</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1424,54 +960,6 @@
         <is>
           <t>bundesliga</t>
         </is>
-      </c>
-      <c r="N10" t="n">
-        <v>23.14285714285714</v>
-      </c>
-      <c r="O10" t="n">
-        <v>184.2857142857143</v>
-      </c>
-      <c r="P10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>495</v>
-      </c>
-      <c r="R10" t="n">
-        <v>105000</v>
-      </c>
-      <c r="S10" t="n">
-        <v>34225000</v>
-      </c>
-      <c r="T10" t="n">
-        <v>542</v>
-      </c>
-      <c r="U10" t="n">
-        <v>9</v>
-      </c>
-      <c r="V10" t="n">
-        <v>26.75</v>
-      </c>
-      <c r="W10" t="n">
-        <v>187.25</v>
-      </c>
-      <c r="X10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>292</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>90000</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>17500000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>304</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:BG17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,32 +465,262 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>competition</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_start_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_start_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_start_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_start_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_away</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
         </is>
       </c>
     </row>
@@ -503,7 +733,12 @@
       <c r="B2" s="2" t="n">
         <v>45604.6875</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reichel t 
+  ger </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">stadion an der alten forsterei
@@ -523,27 +758,169 @@
           <t>fiEQZ7C7</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>59</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>591</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>20242025</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
+      </c>
+      <c r="P2" t="n">
+        <v>27.09090909090909</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>185.8181818181818</v>
+      </c>
+      <c r="R2" t="n">
+        <v>74.45454545454545</v>
+      </c>
+      <c r="S2" t="n">
+        <v>26636.36363636364</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5963636.363636363</v>
+      </c>
+      <c r="U2" t="n">
+        <v>77.27272727272727</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="W2" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>184.1</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>27400</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>11860000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>79</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>28.85714285714286</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>180.7142857142857</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>73.57142857142857</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>27428.57142857143</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>4014285.714285714</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>74.14285714285714</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>26.625</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>183.25</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>72.875</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>22375</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>76.125</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>222</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>89000</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>17100000</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>225</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>420</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>99000</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>23100000</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>451</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +932,12 @@
       <c r="B3" s="2" t="n">
         <v>45605.47916666666</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">vonovia ruhrstadion
@@ -575,27 +957,105 @@
           <t>4jcj2zMd</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="n">
         <v>59</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>591</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>20242025</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>274</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>73000</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>9675000</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>301</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>306</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>246000</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>71000000</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>327</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -607,7 +1067,12 @@
       <c r="B4" s="2" t="n">
         <v>45605.47916666666</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badstubner f 
+  ger </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">mewa arena
@@ -627,27 +1092,105 @@
           <t>nP1i5US1</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
         <v>59</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>591</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>20242025</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>150</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>58000</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>13500000</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>156</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>24.625</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>185.375</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>628</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>352000</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>222200000</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>668</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -659,7 +1202,12 @@
       <c r="B5" s="2" t="n">
         <v>45605.47916666666</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gerach t 
+  ger </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">millerntor stadion
@@ -679,27 +1227,105 @@
           <t>nVp0wiqd</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
         <v>59</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>591</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>20242025</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>23.66666666666667</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>185.3333333333333</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>397</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>77000</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>9940000</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>432</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>368</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>195000</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>67150000</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>412</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -711,7 +1337,12 @@
       <c r="B6" s="2" t="n">
         <v>45605.47916666666</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">storks s 
+  ger </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">weserstadion
@@ -731,27 +1362,105 @@
           <t>63WsD2ei</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
         <v>59</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>591</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>20242025</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>185.25</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>294</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>93000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>305</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>185.25</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>278</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>65000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>288</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -763,7 +1472,12 @@
       <c r="B7" s="2" t="n">
         <v>45605.60416666666</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">red bull arena
@@ -783,27 +1497,105 @@
           <t>88HSzjDr</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="n">
         <v>59</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>591</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>20242025</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>324</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>237000</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>151000000</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>342</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>24.125</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>183.625</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>572</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>137000</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>43225000</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>619</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -835,27 +1627,105 @@
           <t>hQAtP9Sl</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="n">
         <v>59</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>591</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>20242025</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>181.1428571428571</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>508</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>143000</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>26800000</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>518</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>183</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>299</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>119000</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>26900000</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>308</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -867,7 +1737,12 @@
       <c r="B9" s="2" t="n">
         <v>45606.5625</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">mhparena
@@ -887,27 +1762,105 @@
           <t>8vndvXTk</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="n">
         <v>59</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>591</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>20242025</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="n">
+        <v>22.71428571428572</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>183.8571428571429</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>498</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>146000</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>55050000</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>554</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>21.33333333333333</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>197</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>56000</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>9575000</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>234</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -919,7 +1872,12 @@
       <c r="B10" s="2" t="n">
         <v>45606.64583333334</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">osmers h 
+  ger </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">voith arena
@@ -939,28 +1897,792 @@
           <t>nwkTahLL</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="n">
         <v>59</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>591</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>20242025</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="n">
+        <v>22.33333333333333</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>188</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>193</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>44000</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>3875000</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>215</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>23.57142857142857</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>184</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>520</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>241000</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>70800000</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>557</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EuQnZBVQ</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45618.6875</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz arena
+  munich </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>75024</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>59</v>
+      </c>
+      <c r="K11" t="n">
+        <v>591</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2qNaDU87</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45619.47916666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>59</v>
+      </c>
+      <c r="K12" t="n">
+        <v>591</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pOGITkgl</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45619.47916666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>81365</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>59</v>
+      </c>
+      <c r="K13" t="n">
+        <v>591</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>E38ZP7hD</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45619.47916666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>30150</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="n">
+        <v>59</v>
+      </c>
+      <c r="K14" t="n">
+        <v>591</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>fwAoyY0E</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45619.47916666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>60449</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>59</v>
+      </c>
+      <c r="K15" t="n">
+        <v>591</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SrjMmBpK</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45619.47916666666</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>28917</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>59</v>
+      </c>
+      <c r="K16" t="n">
+        <v>591</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>6w5RRTN0</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45619.60416666666</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>58000</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="n">
+        <v>59</v>
+      </c>
+      <c r="K17" t="n">
+        <v>591</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
